--- a/docs/rehearsal/checklist.xlsx
+++ b/docs/rehearsal/checklist.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Checklist!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Checklist!$A$1:$J$143</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Checklist!$A$1:$J$150</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,12 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="766">
   <si>
     <t xml:space="preserve">StayGuard: checklist diễn tập (Gate 1)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cập nhật 03/10/2026 khoảng 11:40 theo kết quả diễn tập và báo cáo của các phiên (142 case; thêm TT-19 đến TT-29, CA-10, CA-11, LO-10, DP-09, DN-13, DN-14, TD-06 đến TD-08). Chưa có chỉnh sửa tay của Khai. Bổ sung sau 11:40 cùng ngày: kết quả các phiên API-1, API-2, WEB-1, WEB-2 và QA tự động, hai ảnh Nhật ký và Giao dịch của Khai. Chỉ TT-25 đánh Đạt (ảnh của Khai); các dòng Lỗi từ QA tự động ghi rõ 'chưa thử tay'.</t>
+    <t xml:space="preserve">Cập nhật 03/10/2026 khoảng 11:40 theo kết quả diễn tập và báo cáo của các phiên (142 case; thêm TT-19 đến TT-29, CA-10, CA-11, LO-10, DP-09, DN-13, DN-14, TD-06 đến TD-08). Chưa có chỉnh sửa tay của Khai. Bổ sung sau 11:40 cùng ngày: kết quả các phiên API-1, API-2, WEB-1, WEB-2 và QA tự động, hai ảnh Nhật ký và Giao dịch của Khai. Chỉ TT-25 đánh Đạt (ảnh của Khai); các dòng Lỗi từ QA tự động ghi rõ 'chưa thử tay'. Từ chiều 03/10: mục tiêu là bản demo cho portfolio, không có khách hàng thật. Các dòng cần SePay thật, ngân hàng thật, máy chủ thật hoặc nghiệp vụ khách hàng đã chuyển Bỏ qua kèm lý do. Thêm GL-13 đến GL-16 cho bản demo. Phạm vi mới (03/10): demo portfolio, không có khách thật. Các mục cần nhà nghỉ thật, tiền thật hoặc hạ tầng thật chuyển sang Bỏ qua kèm lý do; thêm GL-13 đến GL-15 cho phần đóng gói demo.</t>
   </si>
   <si>
     <t xml:space="preserve">Cách dùng</t>
@@ -402,7 +402,9 @@
     <t xml:space="preserve">Lịch sử gửi trả 200 với khóa mới. Khóa cũ không còn dùng ở đâu.</t>
   </si>
   <si>
-    <t xml:space="preserve">Khóa cũ đã dán vào chat: tạo lại khóa trong SePay rồi set-secret lại bằng khóa mới.</t>
+    <t xml:space="preserve">Khóa cũ đã dán vào chat: tạo lại khóa trong SePay rồi set-secret lại bằng khóa mới.
+Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Khóa SePay chỉ là khóa Test mode. Làm khi nối SePay thật.
+Phạm vi demo portfolio, không có khách thật. Khóa của test mode. Đổi nếu dùng lại cho một bản demo công khai.</t>
   </si>
   <si>
     <t xml:space="preserve">CB-08</t>
@@ -417,6 +419,10 @@
     <t xml:space="preserve">Khóa được lưu tách khỏi bản sao lưu database. Mất khóa thì PIN, CCCD, số tài khoản và khóa SePay không đọc lại được.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Dữ liệu demo tạo lại được. Làm khi có dữ liệu thật.
+Phạm vi demo portfolio, không có khách thật. Không có dữ liệu thật cần bảo vệ.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CB-09</t>
   </si>
   <si>
@@ -445,6 +451,9 @@
   </si>
   <si>
     <t xml:space="preserve">PASS: backup-test; số dòng khớp ở mọi bảng (lần trước: 34 bảng).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Làm khi có dữ liệu thật cần giữ.</t>
   </si>
   <si>
     <t xml:space="preserve">CB-11</t>
@@ -595,6 +604,10 @@
     <t xml:space="preserve">Tự thành Đã thanh toán. Biên lai có hai khoản chuyển.</t>
   </si>
   <si>
+    <t xml:space="preserve">QA tự động + đọc code (chưa thử tay): biên lai chỉ có một dòng chuyển khoản cộng dồn vì ListReceiptPayments chỉ lấy thanh toán PAID; dòng chuyển thiếu vẫn là MISMATCH trong Cần xử lý sau khi phiếu đã thanh toán. Giao API-2.
+QA tự động: biên lai chỉ có một dòng chuyển khoản cộng dồn, không phải hai; khoản chuyển thiếu vẫn nằm ở Cần xử lý sau khi phiếu đã trả. Đọc code: ListReceiptPayments chỉ lấy thanh toán PAID, mỗi thanh toán một dòng. Giao API-2.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TT-09</t>
   </si>
   <si>
@@ -634,7 +647,9 @@
   </si>
   <si>
     <t xml:space="preserve">Hiện nút Tiền ra đang bị xám vì webhook chỉ nghe Tiền vào.
-QA tự động + đọc code, chưa thử tay: tiền ra được lưu thành 'Chưa rõ phiếu' và gán được vào phiếu (InsertPaymentEvent luôn ghi UNMATCHED). Giao API-2 (kết quả IGNORED).</t>
+QA tự động + đọc code, chưa thử tay: tiền ra được lưu thành 'Chưa rõ phiếu' và gán được vào phiếu (InsertPaymentEvent luôn ghi UNMATCHED). Giao API-2 (kết quả IGNORED).
+Đã sửa (API-2 2b9b88f: tiền ra ghi IGNORED, không hiện, không gán được). QA tự động đạt trên bản build mới. Dòng đã lưu trước migration 0031 không phân loại được lại.
+Đã sửa (API-2 2b9b88f / API-1 185a589, b7aa449 / WEB-2 e174d33, 695a060). QA tự động đạt trên bản mới. Thử lại sau rebuild.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-12</t>
@@ -701,7 +716,9 @@
     <t xml:space="preserve">Đúng tài khoản, số tiền, nội dung = mã phiếu. Ghi vào Ghi chú: ô số tiền và nội dung của từng ngân hàng có sửa được không.</t>
   </si>
   <si>
-    <t xml:space="preserve">Màn QR lễ tân hiện số tài khoản chính *******0001. Tài khoản Vietcombank hộ kinh doanh bắt buộc VA: xem GL-04.</t>
+    <t xml:space="preserve">Màn QR lễ tân hiện số tài khoản chính *******0001. Tài khoản Vietcombank hộ kinh doanh bắt buộc VA: xem GL-04.
+Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Cần ngân hàng thật. Demo dùng nút Giả lập tiền về.
+Phạm vi demo portfolio, không có khách thật. Không cần app ngân hàng thật; QR test mode đủ cho demo.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-17</t>
@@ -718,7 +735,8 @@
   </si>
   <si>
     <t xml:space="preserve">Tùy chọn.
-Nghi cùng nguyên nhân TT-11 (đọc code): tiền vào tài khoản lạ cũng lưu UNMATCHED. Chưa kiểm chứng.</t>
+Đã sửa (API-2 2b9b88f: tiền vào tài khoản lạ ghi IGNORED). QA báo lỗi nhưng bài test so với mọi dòng Chưa rõ phiếu cùng số tiền trong nhà nghỉ dùng chung; QA sửa test (số tiền riêng, so số dòng trước và sau).
+Đã sửa (API-2 2b9b88f). Test QA bị lỗi: so khớp theo số tiền và vướng các dòng UNMATCHED do spec khác để lại; QA đổi sang số tiền riêng.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-18</t>
@@ -890,7 +908,9 @@
     <t xml:space="preserve">QR trỏ về VA. Webhook khớp theo trường VA. Phiếu thành Đã thanh toán.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hiện QR trỏ số tài khoản chính (*0001). Prompt VA cho API-1 có thể chưa được giao. Cần biết loại tài khoản của nhà nghỉ thật (GL-04).</t>
+    <t xml:space="preserve">Hiện QR trỏ số tài khoản chính (*0001). Prompt VA cho API-1 có thể chưa được giao. Cần biết loại tài khoản của nhà nghỉ thật (GL-04).
+Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Nhà nghỉ thật chưa có; làm khi nối ngân hàng bắt buộc VA (ví dụ BIDV).
+Phạm vi demo portfolio, không có khách thật. Không có nhà nghỉ thật; test mode SePay chạy bằng số tài khoản chính. Làm khi có khách dùng ngân hàng bắt buộc VA (ví dụ BIDV).</t>
   </si>
   <si>
     <t xml:space="preserve">TT-29</t>
@@ -1134,6 +1154,9 @@
     <t xml:space="preserve">Khổ 80 mm. Không in nút bấm. Có tên nhà nghỉ, mã phiếu, các khoản thanh toán.</t>
   </si>
   <si>
+    <t xml:space="preserve">print.spec.ts kiểm khổ 80 mm bằng PDF; không cần máy in thật.</t>
+  </si>
+  <si>
     <t xml:space="preserve">LO-07</t>
   </si>
   <si>
@@ -1348,7 +1371,9 @@
     <t xml:space="preserve">Số hiện dạng che. Hiện lộ đủ số. Nhật ký có dòng GUEST_ID.</t>
   </si>
   <si>
-    <t xml:space="preserve">QA GI-02 + đọc code, chưa thử tay: nhật ký xem CCCD có ghi nhưng xếp nhóm Giá và cài đặt, lọc Giấy tờ khách không ra. Cả 8 mã GUEST_ID_* và 2 mã INSTALLER_* bị sai nhóm (tiền tố chữ hoa). Giao API-1.</t>
+    <t xml:space="preserve">QA GI-02 + đọc code, chưa thử tay: nhật ký xem CCCD có ghi nhưng xếp nhóm Giá và cài đặt, lọc Giấy tờ khách không ra. Cả 8 mã GUEST_ID_* và 2 mã INSTALLER_* bị sai nhóm (tiền tố chữ hoa). Giao API-1.
+Đã sửa (API-1 185a589): mọi mã GUEST_ID_* và INSTALLER_* nằm đúng nhóm; thêm test duyệt mọi mã thao tác.
+Đã sửa (API-2 2b9b88f / API-1 185a589, b7aa449 / WEB-2 e174d33, 695a060). QA tự động đạt trên bản mới. Thử lại sau rebuild.</t>
   </si>
   <si>
     <t xml:space="preserve">GT-04</t>
@@ -1654,7 +1679,9 @@
     <t xml:space="preserve">Có đủ thao tác quan trọng (sửa giờ, gán tiền, xem CCCD, đổi quyền). Không sửa hoặc xóa được.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ảnh Nhật ký 03/10: dòng 'Thanh toán xong {room}', 'Tạo thanh toán {room}', 'Trả phòng {room}', 'Nhận phòng {room}' hiện nguyên {room}; cột Người trống ở dòng 10:12 (thao tác của hệ thống). Nguyên nhân: API không ghi số phòng vào nhật ký; thêm 27 mã thao tác chưa có câu mô tả (đọc code). Giao API-1 (room, bill) và WEB-2 (câu mô tả).</t>
+    <t xml:space="preserve">Ảnh Nhật ký 03/10: dòng 'Thanh toán xong {room}', 'Tạo thanh toán {room}', 'Trả phòng {room}', 'Nhận phòng {room}' hiện nguyên {room}; cột Người trống ở dòng 10:12 (thao tác của hệ thống). Nguyên nhân: API không ghi số phòng vào nhật ký; thêm 27 mã thao tác chưa có câu mô tả (đọc code). Giao API-1 (room, bill) và WEB-2 (câu mô tả).
+Đã sửa (API-1 b7aa449 điền room, bill; WEB-2 e174d33, 695a060 mô tả đủ 57 thao tác, người trống hiện Hệ thống). QA UI-01 đạt ở /owner/activity.
+Đã sửa (API-2 2b9b88f / API-1 185a589, b7aa449 / WEB-2 e174d33, 695a060). QA tự động đạt trên bản mới. Thử lại sau rebuild.</t>
   </si>
   <si>
     <t xml:space="preserve">TD-05</t>
@@ -1891,7 +1918,9 @@
   </si>
   <si>
     <t xml:space="preserve">SePay thử lại tối đa 7 lần trong khoảng 33 phút.
-QA tự động: webhook ký lại, thời điểm 6 phút trước, gửi sau khi API khởi động lại bị từ chối 401 (quá 300 giây). SePay gửi lại thật vẫn cần thử tay.</t>
+QA tự động: webhook ký lại, thời điểm 6 phút trước, gửi sau khi API khởi động lại bị từ chối 401 (quá 300 giây). SePay gửi lại thật vẫn cần thử tay.
+Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Cần SePay thật. Webhook quá hạn đã có test tự động (QA).
+Bộ test tự động đủ cho demo; thử SePay gửi lại thật là tùy chọn.</t>
   </si>
   <si>
     <t xml:space="preserve">BM-05</t>
@@ -1918,6 +1947,10 @@
     <t xml:space="preserve">File .dump có trong bucket. Khôi phục thử vào database tạm khớp số dòng.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Cần S3 thật. Làm khi có dữ liệu thật.
+Phạm vi demo portfolio, không có khách thật. Không có dữ liệu thật cần sao lưu lên S3.</t>
+  </si>
+  <si>
     <t xml:space="preserve">VH-02</t>
   </si>
   <si>
@@ -1957,6 +1990,10 @@
     <t xml:space="preserve">Chỉ có form đăng nhập, không có Thử với vai trò.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Ngược với mục tiêu: bản portfolio bật chế độ demo (bộ chọn vai trò, Giả lập tiền về). Xem GL-13.
+Phạm vi demo portfolio, không có khách thật. Ngược mục tiêu: bản demo giữ bộ chọn vai trò.</t>
+  </si>
+  <si>
     <t xml:space="preserve">VH-05</t>
   </si>
   <si>
@@ -1993,6 +2030,10 @@
     <t xml:space="preserve">Container và volume của stayguard-rehearse bị xóa.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Không còn stack diễn tập riêng; QA tự tạo nhà nghỉ mới mỗi lần chạy.
+Phạm vi demo portfolio, không có khách thật. Không cần dọn khi chưa có bản thật.</t>
+  </si>
+  <si>
     <t xml:space="preserve">GD-01</t>
   </si>
   <si>
@@ -2101,7 +2142,8 @@
     <t xml:space="preserve">/readyz trả 200. Chứng chỉ HTTPS hợp lệ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Oracle Free hết máy ARM; dự phòng là VPS trả phí ở Singapore.</t>
+    <t xml:space="preserve">Oracle Free hết máy ARM; dự phòng là VPS trả phí ở Singapore.
+Tùy chọn: chỉ cần nếu muốn có đường dẫn demo công khai cho portfolio.</t>
   </si>
   <si>
     <t xml:space="preserve">GL-03</t>
@@ -2116,6 +2158,10 @@
     <t xml:space="preserve">Khóa không nằm trong git và không nằm cùng bản sao lưu.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Không có môi trường production thật.
+Phạm vi demo portfolio, không có khách thật. Không có production thật.</t>
+  </si>
+  <si>
     <t xml:space="preserve">GL-04</t>
   </si>
   <si>
@@ -2128,7 +2174,9 @@
     <t xml:space="preserve">Nếu bắt buộc VA: đã có tính năng lưu VA, QR trỏ về VA, webhook khớp VA, và đã thử với dữ liệu VA. Nếu không: ghi Không bắt buộc VA.</t>
   </si>
   <si>
-    <t xml:space="preserve">Test mode: Vietcombank hộ kinh doanh bắt buộc VA, QR hiện đang trỏ số tài khoản chính. Cần hỏi nhà nghỉ thật dùng loại tài khoản gì và xác nhận API-1 đã làm VA.</t>
+    <t xml:space="preserve">Test mode: Vietcombank hộ kinh doanh bắt buộc VA, QR hiện đang trỏ số tài khoản chính. Cần hỏi nhà nghỉ thật dùng loại tài khoản gì và xác nhận API-1 đã làm VA.
+Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Không có nhà nghỉ thật để hỏi. Xem TT-28.
+Phạm vi demo portfolio, không có khách thật. Không có nhà nghỉ thật.</t>
   </si>
   <si>
     <t xml:space="preserve">GL-05</t>
@@ -2143,6 +2191,10 @@
     <t xml:space="preserve">Đủ nhà nghỉ, phòng, giá, dịch vụ, tài khoản, nhân viên. PIN một lần được in ra.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Không có nhà nghỉ thật.
+Phạm vi demo portfolio, không có khách thật. Không có nhà nghỉ thật.</t>
+  </si>
+  <si>
     <t xml:space="preserve">GL-06</t>
   </si>
   <si>
@@ -2155,6 +2207,10 @@
     <t xml:space="preserve">sepay status: CONNECTED, chữ ký hợp lệ.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Không có chủ nhà nghỉ thật.
+Phạm vi demo portfolio, không có khách thật. Không dùng SePay thật; chỉ test mode.</t>
+  </si>
+  <si>
     <t xml:space="preserve">GL-07</t>
   </si>
   <si>
@@ -2167,6 +2223,10 @@
     <t xml:space="preserve">Phiếu tự Đã thanh toán. Tiền về tài khoản chủ.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Không chuyển tiền thật.
+Phạm vi demo portfolio, không có khách thật. Không chuyển tiền thật.</t>
+  </si>
+  <si>
     <t xml:space="preserve">GL-08</t>
   </si>
   <si>
@@ -2191,6 +2251,10 @@
     <t xml:space="preserve">Mọi người đăng nhập được.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Không có nhân viên thật.
+Phạm vi demo portfolio, không có khách thật. Luồng đặt PIN lần đầu đã có ở CB-09.</t>
+  </si>
+  <si>
     <t xml:space="preserve">GL-10</t>
   </si>
   <si>
@@ -2206,6 +2270,10 @@
     <t xml:space="preserve">Họ tự làm một lượt nhận phòng, trả phòng, thu tiền, kết ca.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Không có lễ tân thật.
+Phạm vi demo portfolio, không có khách thật. Không có lễ tân thật.</t>
+  </si>
+  <si>
     <t xml:space="preserve">GL-11</t>
   </si>
   <si>
@@ -2218,6 +2286,10 @@
     <t xml:space="preserve">Chốt số ngày tự xóa và nội dung thông báo cho khách.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Khi có khách thật mới cần hỏi người có chuyên môn; demo vẫn giữ dòng thông báo.
+Phạm vi demo portfolio, không có khách thật. Chỉ dùng dữ liệu giả; ghi rõ trong README.</t>
+  </si>
+  <si>
     <t xml:space="preserve">GL-12</t>
   </si>
   <si>
@@ -2228,6 +2300,107 @@
   </si>
   <si>
     <t xml:space="preserve">Có file mới mỗi ngày. Khôi phục thử khớp số dòng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bỏ qua: dự án là bản demo cho portfolio, không có khách hàng thật. Dữ liệu demo tạo lại được.
+Phạm vi demo portfolio, không có khách thật. Không có dữ liệu thật.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lễ tân, Chủ, Buồng phòng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kịch bản demo 3 phút chạy trọn vẹn, không cần SePay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Mở /vi, chọn Lễ tân: nhận phòng A102, trả phòng A101 (đã có 2 nước suối)
+2) Thanh toán QR, bấm Giả lập tiền về
+3) Chọn Buồng phòng, bấm Dọn xong
+4) Chọn Chủ nhà nghỉ: xem Tổng quan và Giao dịch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đúng từng bước README mục 5: màn QR tự chuyển Đã thanh toán, phòng sang Cần dọn, doanh thu và Giao dịch cập nhật. Chạy ở 390 và 1280 px, tiếng Việt và tiếng Anh, không lỗi console.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chưa có test tự động nào phủ đường /v1/demo/sessions và nút Giả lập tiền về; QA thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dữ liệu demo đủ để mọi màn của chủ có nội dung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chọn Chủ nhà nghỉ trong chế độ demo, mở lần lượt Tổng quan, Giao dịch, Lượt ở, Đối soát ca, Báo cáo, Chi phí, Bảng lương, Bảo trì, Dịch vụ và kho, Lịch ca, Cảnh báo, Nhật ký</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không màn nào trống hoặc toàn số 0. Có dữ liệu khoảng 30 ngày: lượt ở, thanh toán chuyển khoản và tiền mặt, ca đã kết, chi phí, phiếu bảo trì, lịch ca, nghỉ phép, bảng lương, vài cảnh báo (cả đã giải quyết).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hạt giống hiện chỉ có 2 tòa, 5 dịch vụ, 5 người dùng, 5 lượt ở mẫu, 2 cảnh báo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mỗi lượt vào demo có dữ liệu riêng và tự dọn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Vào demo ở hai trình duyệt khác nhau, làm vài thao tác ở trình duyệt A
+2) Xem dữ liệu ở trình duyệt B
+3) Để tài khoản dùng thử hết hạn hoặc chạy lệnh dọn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hai phiên không thấy dữ liệu của nhau. Nhà nghỉ thử hết hạn bị dọn, không làm đầy cơ sở dữ liệu. Nhà nghỉ khác không bị ảnh hưởng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API-2 kiểm tra đã có job dọn nhà nghỉ thử hết hạn chưa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gói giới thiệu portfolio: README, ảnh chụp, video kịch bản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mở README trên GitHub; mở thư mục ảnh; xem video hoặc GIF kịch bản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">README có mô tả sản phẩm, sơ đồ kiến trúc (Go, PostgreSQL RLS, Next.js nhúng vào binary), lệnh chạy demo, ảnh các màn chính, video hoặc GIF 3 phút, và các quyết định kỹ thuật nổi bật (tiền số nguyên, webhook ký HMAC, idempotency, RLS, nhật ký không sửa được).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dùng lại script chụp ảnh của QA và quay video bằng Playwright.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">README, ảnh chụp màn hình và kịch bản demo 3 phút</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) README: mô tả sản phẩm, kiến trúc, cách chạy local
+2) Ảnh chụp 6 đến 8 màn chính (vi) và một GIF luồng thanh toán
+3) Kịch bản demo: các bước và vai trò</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Người lạ chạy được app trong 10 phút theo README. Có ảnh, GIF và kịch bản. Ghi rõ dữ liệu là giả.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đặt lại dữ liệu demo bằng một lệnh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chạy lệnh đặt lại dữ liệu demo, mở app, chọn từng vai trò</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Có đủ phòng, lượt ở, giao dịch mẫu để xem ngay. Chạy lại lệnh thì về đúng trạng thái đó.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luồng SePay test mode quay thành video ngắn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chạy tunnel, tạo giao dịch mô phỏng ở SePay test mode, quay màn lễ tân và chủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video 1 đến 2 phút: QR, tiền về qua webhook, phiếu Đã thanh toán, chuyển thiếu rồi bù. Không lộ khóa, mã hook hay số tài khoản.</t>
   </si>
 </sst>
 </file>
@@ -2598,7 +2771,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="25">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2747,6 +2920,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFE0DED8"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF5C2BD"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -2772,6 +2953,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF1F5A30"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5C5A55"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3374,15 +3563,15 @@
       </c>
       <c r="F5" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A5,Checklist!$H$2:$H$300,"Bỏ qua")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" s="9" t="n">
         <f aca="false">B5-C5-D5-E5-F5</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H5" s="10" t="n">
         <f aca="false">IFERROR(C5/(B5-F5),0)</f>
-        <v>0.454545454545455</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3403,19 +3592,19 @@
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A6,Checklist!$H$2:$H$300,"Chờ thử lại")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A6,Checklist!$H$2:$H$300,"Bỏ qua")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">B6-C6-D6-E6-F6</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">IFERROR(C6/(B6-F6),0)</f>
-        <v>0.275862068965517</v>
+        <v>0.296296296296296</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3531,11 +3720,11 @@
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A10,Checklist!$H$2:$H$300,"Lỗi")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A10,Checklist!$H$2:$H$300,"Chờ thử lại")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A10,Checklist!$H$2:$H$300,"Bỏ qua")</f>
@@ -3597,11 +3786,11 @@
       </c>
       <c r="D12" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A12,Checklist!$H$2:$H$300,"Lỗi")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A12,Checklist!$H$2:$H$300,"Chờ thử lại")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A12,Checklist!$H$2:$H$300,"Bỏ qua")</f>
@@ -3671,11 +3860,11 @@
       </c>
       <c r="F14" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A14,Checklist!$H$2:$H$300,"Bỏ qua")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">B14-C14-D14-E14-F14</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H14" s="10" t="n">
         <f aca="false">IFERROR(C14/(B14-F14),0)</f>
@@ -3704,11 +3893,11 @@
       </c>
       <c r="F15" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A15,Checklist!$H$2:$H$300,"Bỏ qua")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">B15-C15-D15-E15-F15</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H15" s="10" t="n">
         <f aca="false">IFERROR(C15/(B15-F15),0)</f>
@@ -3754,7 +3943,7 @@
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$300,$A17)</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C17" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A17,Checklist!$H$2:$H$300,"Đạt")</f>
@@ -3770,11 +3959,11 @@
       </c>
       <c r="F17" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A17,Checklist!$H$2:$H$300,"Bỏ qua")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G17" s="9" t="n">
         <f aca="false">B17-C17-D17-E17-F17</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H17" s="10" t="n">
         <f aca="false">IFERROR(C17/(B17-F17),0)</f>
@@ -3787,7 +3976,7 @@
       </c>
       <c r="B18" s="18" t="n">
         <f aca="false">SUM(B5:B17)</f>
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">SUM(C5:C17)</f>
@@ -3795,23 +3984,23 @@
       </c>
       <c r="D18" s="18" t="n">
         <f aca="false">SUM(D5:D17)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="18" t="n">
         <f aca="false">SUM(E5:E17)</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">SUM(F5:F17)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G18" s="18" t="n">
         <f aca="false">SUM(G5:G17)</f>
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">IFERROR(C18/(B18-F18),0)</f>
-        <v>0.119718309859155</v>
+        <v>0.130769230769231</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3825,7 +4014,7 @@
       </c>
       <c r="B21" s="21" t="n">
         <f aca="false">COUNTIFS(Checklist!$G$2:$G$300,"Cao")-COUNTIFS(Checklist!$G$2:$G$300,"Cao",Checklist!$H$2:$H$300,"Đạt")-COUNTIFS(Checklist!$G$2:$G$300,"Cao",Checklist!$H$2:$H$300,"Bỏ qua")</f>
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3834,7 +4023,7 @@
       </c>
       <c r="B22" s="21" t="n">
         <f aca="false">D18</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3898,7 +4087,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J143"/>
+  <dimension ref="A1:J150"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -4154,7 +4343,7 @@
         <v>93</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I8" s="32"/>
       <c r="J8" s="33" t="s">
@@ -4184,32 +4373,34 @@
         <v>93</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I9" s="32"/>
-      <c r="J9" s="33"/>
+      <c r="J9" s="33" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B10" s="27" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H10" s="31" t="s">
         <v>61</v>
@@ -4219,7 +4410,7 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B11" s="27" t="s">
         <v>63</v>
@@ -4228,44 +4419,48 @@
         <v>89</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G11" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="32"/>
-      <c r="J11" s="33"/>
+        <v>60</v>
+      </c>
+      <c r="I11" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B12" s="27" t="s">
         <v>63</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H12" s="31" t="s">
         <v>61</v>
@@ -4275,22 +4470,22 @@
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G13" s="30" t="s">
         <v>93</v>
@@ -4302,27 +4497,27 @@
         <v>46298</v>
       </c>
       <c r="J13" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G14" s="30" t="s">
         <v>93</v>
@@ -4334,27 +4529,27 @@
         <v>46298</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G15" s="30" t="s">
         <v>93</v>
@@ -4366,27 +4561,27 @@
         <v>46298</v>
       </c>
       <c r="J15" s="33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G16" s="30" t="s">
         <v>93</v>
@@ -4398,27 +4593,27 @@
         <v>46298</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B17" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G17" s="30" t="s">
         <v>93</v>
@@ -4428,27 +4623,27 @@
       </c>
       <c r="I17" s="32"/>
       <c r="J17" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B18" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G18" s="30" t="s">
         <v>93</v>
@@ -4461,22 +4656,22 @@
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B19" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G19" s="30" t="s">
         <v>93</v>
@@ -4489,50 +4684,54 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G20" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I20" s="32"/>
-      <c r="J20" s="33"/>
+        <v>58</v>
+      </c>
+      <c r="I20" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J20" s="33" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G21" s="30" t="s">
         <v>93</v>
@@ -4545,22 +4744,22 @@
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G22" s="30" t="s">
         <v>93</v>
@@ -4573,57 +4772,55 @@
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G23" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="I23" s="32" t="n">
-        <v>46298</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="I23" s="32"/>
       <c r="J23" s="33" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B24" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G24" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H24" s="31" t="s">
         <v>61</v>
@@ -4633,22 +4830,22 @@
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B25" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G25" s="30" t="s">
         <v>93</v>
@@ -4660,27 +4857,27 @@
         <v>46298</v>
       </c>
       <c r="J25" s="33" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B26" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G26" s="30" t="s">
         <v>93</v>
@@ -4692,30 +4889,30 @@
         <v>46298</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B27" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D27" s="29" t="s">
         <v>40</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G27" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H27" s="31" t="s">
         <v>61</v>
@@ -4725,85 +4922,85 @@
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B28" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G28" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I28" s="32"/>
       <c r="J28" s="33" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B29" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I29" s="32"/>
       <c r="J29" s="33" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B30" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G30" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H30" s="31" t="s">
         <v>61</v>
@@ -4813,22 +5010,22 @@
     </row>
     <row r="31" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="26" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B31" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G31" s="30" t="s">
         <v>93</v>
@@ -4838,27 +5035,27 @@
       </c>
       <c r="I31" s="32"/>
       <c r="J31" s="33" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="26" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B32" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G32" s="30" t="s">
         <v>93</v>
@@ -4870,27 +5067,27 @@
         <v>46298</v>
       </c>
       <c r="J32" s="33" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B33" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="G33" s="30" t="s">
         <v>93</v>
@@ -4900,27 +5097,27 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="26" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B34" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G34" s="30" t="s">
         <v>93</v>
@@ -4930,27 +5127,27 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B35" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G35" s="30" t="s">
         <v>93</v>
@@ -4960,27 +5157,27 @@
       </c>
       <c r="I35" s="32"/>
       <c r="J35" s="33" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B36" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G36" s="30" t="s">
         <v>93</v>
@@ -4990,30 +5187,30 @@
       </c>
       <c r="I36" s="32"/>
       <c r="J36" s="33" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="26" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B37" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G37" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H37" s="31" t="s">
         <v>12</v>
@@ -5022,27 +5219,27 @@
         <v>46298</v>
       </c>
       <c r="J37" s="33" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="26" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B38" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G38" s="30" t="s">
         <v>93</v>
@@ -5052,27 +5249,27 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="33" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="26" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B39" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G39" s="30" t="s">
         <v>93</v>
@@ -5082,57 +5279,57 @@
       </c>
       <c r="I39" s="32"/>
       <c r="J39" s="33" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B40" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G40" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B41" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G41" s="30" t="s">
         <v>93</v>
@@ -5142,27 +5339,27 @@
       </c>
       <c r="I41" s="32"/>
       <c r="J41" s="33" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B42" s="35" t="s">
         <v>65</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G42" s="30" t="s">
         <v>93</v>
@@ -5174,27 +5371,27 @@
         <v>46298</v>
       </c>
       <c r="J42" s="33" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="26" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B43" s="35" t="s">
         <v>65</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G43" s="30" t="s">
         <v>93</v>
@@ -5207,22 +5404,22 @@
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B44" s="35" t="s">
         <v>65</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F44" s="28" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G44" s="30" t="s">
         <v>93</v>
@@ -5235,22 +5432,22 @@
     </row>
     <row r="45" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B45" s="35" t="s">
         <v>65</v>
       </c>
       <c r="C45" s="28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E45" s="28" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F45" s="28" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G45" s="30" t="s">
         <v>93</v>
@@ -5260,27 +5457,27 @@
       </c>
       <c r="I45" s="32"/>
       <c r="J45" s="33" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="26" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B46" s="35" t="s">
         <v>65</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G46" s="30" t="s">
         <v>93</v>
@@ -5293,22 +5490,22 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B47" s="35" t="s">
         <v>65</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G47" s="30" t="s">
         <v>93</v>
@@ -5321,55 +5518,55 @@
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="26" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B48" s="35" t="s">
         <v>65</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F48" s="28" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G48" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H48" s="31" t="s">
         <v>61</v>
       </c>
       <c r="I48" s="32"/>
       <c r="J48" s="33" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="26" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B49" s="35" t="s">
         <v>65</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E49" s="28" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F49" s="28" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G49" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H49" s="31" t="s">
         <v>61</v>
@@ -5379,25 +5576,25 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B50" s="35" t="s">
         <v>65</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F50" s="28" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G50" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H50" s="31" t="s">
         <v>61</v>
@@ -5407,22 +5604,22 @@
     </row>
     <row r="51" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B51" s="35" t="s">
         <v>65</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F51" s="28" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G51" s="30" t="s">
         <v>93</v>
@@ -5432,57 +5629,57 @@
       </c>
       <c r="I51" s="32"/>
       <c r="J51" s="33" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B52" s="35" t="s">
         <v>65</v>
       </c>
       <c r="C52" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E52" s="28" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F52" s="28" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G52" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H52" s="31" t="s">
         <v>59</v>
       </c>
       <c r="I52" s="32"/>
       <c r="J52" s="33" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="26" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B53" s="36" t="s">
         <v>66</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F53" s="28" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G53" s="30" t="s">
         <v>93</v>
@@ -5494,30 +5691,30 @@
         <v>46298</v>
       </c>
       <c r="J53" s="33" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="26" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B54" s="36" t="s">
         <v>66</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E54" s="28" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F54" s="28" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G54" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H54" s="31" t="s">
         <v>61</v>
@@ -5527,22 +5724,22 @@
     </row>
     <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B55" s="36" t="s">
         <v>66</v>
       </c>
       <c r="C55" s="28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D55" s="29" t="s">
         <v>46</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F55" s="28" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G55" s="30" t="s">
         <v>93</v>
@@ -5555,22 +5752,22 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="26" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B56" s="36" t="s">
         <v>66</v>
       </c>
       <c r="C56" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E56" s="28" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F56" s="28" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G56" s="30" t="s">
         <v>93</v>
@@ -5583,25 +5780,25 @@
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="26" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B57" s="36" t="s">
         <v>66</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F57" s="28" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G57" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H57" s="31" t="s">
         <v>61</v>
@@ -5611,53 +5808,55 @@
     </row>
     <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="26" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B58" s="36" t="s">
         <v>66</v>
       </c>
       <c r="C58" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F58" s="28" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G58" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H58" s="31" t="s">
         <v>61</v>
       </c>
       <c r="I58" s="32"/>
-      <c r="J58" s="33"/>
+      <c r="J58" s="33" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="26" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B59" s="36" t="s">
         <v>66</v>
       </c>
       <c r="C59" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F59" s="28" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="G59" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H59" s="31" t="s">
         <v>12</v>
@@ -5666,30 +5865,30 @@
         <v>46298</v>
       </c>
       <c r="J59" s="33" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="26" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B60" s="36" t="s">
         <v>66</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F60" s="28" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G60" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H60" s="31" t="s">
         <v>61</v>
@@ -5699,25 +5898,25 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="26" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B61" s="36" t="s">
         <v>66</v>
       </c>
       <c r="C61" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F61" s="28" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G61" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H61" s="31" t="s">
         <v>61</v>
@@ -5727,25 +5926,25 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="26" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B62" s="36" t="s">
         <v>66</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F62" s="28" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="G62" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H62" s="31" t="s">
         <v>12</v>
@@ -5754,27 +5953,27 @@
         <v>46298</v>
       </c>
       <c r="J62" s="33" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="26" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B63" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C63" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F63" s="28" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G63" s="30" t="s">
         <v>93</v>
@@ -5787,22 +5986,22 @@
     </row>
     <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="26" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B64" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E64" s="28" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F64" s="28" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="G64" s="30" t="s">
         <v>93</v>
@@ -5815,22 +6014,22 @@
     </row>
     <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="26" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B65" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F65" s="28" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="G65" s="30" t="s">
         <v>93</v>
@@ -5843,22 +6042,22 @@
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="26" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B66" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F66" s="28" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G66" s="30" t="s">
         <v>93</v>
@@ -5871,25 +6070,25 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="26" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B67" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E67" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F67" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="G67" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H67" s="31" t="s">
         <v>61</v>
@@ -5899,22 +6098,22 @@
     </row>
     <row r="68" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="26" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B68" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C68" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D68" s="29" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F68" s="28" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G68" s="30" t="s">
         <v>93</v>
@@ -5927,25 +6126,25 @@
     </row>
     <row r="69" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="26" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B69" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E69" s="28" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F69" s="28" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="G69" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H69" s="31" t="s">
         <v>61</v>
@@ -5955,25 +6154,25 @@
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="26" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B70" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C70" s="28" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F70" s="28" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="G70" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H70" s="31" t="s">
         <v>61</v>
@@ -5983,22 +6182,22 @@
     </row>
     <row r="71" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="26" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B71" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D71" s="29" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E71" s="28" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F71" s="28" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="G71" s="30" t="s">
         <v>93</v>
@@ -6008,27 +6207,27 @@
       </c>
       <c r="I71" s="32"/>
       <c r="J71" s="33" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="26" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B72" s="38" t="s">
         <v>68</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D72" s="29" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F72" s="28" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="G72" s="30" t="s">
         <v>93</v>
@@ -6041,22 +6240,22 @@
     </row>
     <row r="73" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="26" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B73" s="38" t="s">
         <v>68</v>
       </c>
       <c r="C73" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F73" s="28" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="G73" s="30" t="s">
         <v>93</v>
@@ -6069,54 +6268,52 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="26" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B74" s="38" t="s">
         <v>68</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E74" s="28" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F74" s="28" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="G74" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H74" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="I74" s="32" t="n">
-        <v>46298</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="I74" s="32"/>
       <c r="J74" s="33" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="26" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B75" s="38" t="s">
         <v>68</v>
       </c>
       <c r="C75" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D75" s="29" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E75" s="28" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F75" s="28" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="G75" s="30" t="s">
         <v>93</v>
@@ -6129,22 +6326,22 @@
     </row>
     <row r="76" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="26" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B76" s="38" t="s">
         <v>68</v>
       </c>
       <c r="C76" s="28" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F76" s="28" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="G76" s="30" t="s">
         <v>93</v>
@@ -6157,22 +6354,22 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="26" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B77" s="38" t="s">
         <v>68</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E77" s="28" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F77" s="28" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="G77" s="30" t="s">
         <v>93</v>
@@ -6185,25 +6382,25 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="26" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B78" s="38" t="s">
         <v>68</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D78" s="29" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E78" s="28" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F78" s="28" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="G78" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H78" s="31" t="s">
         <v>61</v>
@@ -6213,7 +6410,7 @@
     </row>
     <row r="79" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="26" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B79" s="38" t="s">
         <v>68</v>
@@ -6222,13 +6419,13 @@
         <v>89</v>
       </c>
       <c r="D79" s="29" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E79" s="28" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="F79" s="28" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G79" s="30" t="s">
         <v>93</v>
@@ -6238,12 +6435,12 @@
       </c>
       <c r="I79" s="32"/>
       <c r="J79" s="33" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="26" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B80" s="38" t="s">
         <v>68</v>
@@ -6252,16 +6449,16 @@
         <v>89</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E80" s="28" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F80" s="28" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G80" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H80" s="31" t="s">
         <v>61</v>
@@ -6271,22 +6468,22 @@
     </row>
     <row r="81" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="26" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B81" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C81" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E81" s="28" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="G81" s="30" t="s">
         <v>93</v>
@@ -6299,22 +6496,22 @@
     </row>
     <row r="82" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="26" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B82" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F82" s="28" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="G82" s="30" t="s">
         <v>93</v>
@@ -6327,22 +6524,22 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="26" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B83" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C83" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D83" s="29" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E83" s="28" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F83" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="G83" s="30" t="s">
         <v>93</v>
@@ -6355,22 +6552,22 @@
     </row>
     <row r="84" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="26" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B84" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C84" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E84" s="28" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F84" s="28" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="G84" s="30" t="s">
         <v>93</v>
@@ -6383,22 +6580,22 @@
     </row>
     <row r="85" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="26" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B85" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C85" s="28" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E85" s="28" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="F85" s="28" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="G85" s="30" t="s">
         <v>93</v>
@@ -6411,22 +6608,22 @@
     </row>
     <row r="86" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="26" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B86" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C86" s="28" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F86" s="28" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="G86" s="30" t="s">
         <v>93</v>
@@ -6439,22 +6636,22 @@
     </row>
     <row r="87" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="26" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B87" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C87" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E87" s="28" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F87" s="28" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G87" s="30" t="s">
         <v>93</v>
@@ -6464,27 +6661,27 @@
       </c>
       <c r="I87" s="32"/>
       <c r="J87" s="33" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="26" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B88" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C88" s="28" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E88" s="28" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F88" s="28" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="G88" s="30" t="s">
         <v>93</v>
@@ -6497,22 +6694,22 @@
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="26" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B89" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="E89" s="28" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="F89" s="28" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="G89" s="30" t="s">
         <v>93</v>
@@ -6525,25 +6722,25 @@
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="26" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B90" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C90" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E90" s="28" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="F90" s="28" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="G90" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H90" s="31" t="s">
         <v>61</v>
@@ -6553,25 +6750,25 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="26" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B91" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C91" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D91" s="29" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E91" s="28" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F91" s="28" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="G91" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H91" s="31" t="s">
         <v>61</v>
@@ -6581,25 +6778,25 @@
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="26" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B92" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C92" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D92" s="29" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E92" s="28" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F92" s="28" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="G92" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H92" s="31" t="s">
         <v>61</v>
@@ -6609,52 +6806,52 @@
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="26" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B93" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C93" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D93" s="29" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="E93" s="28" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F93" s="28" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="G93" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H93" s="31" t="s">
         <v>59</v>
       </c>
       <c r="I93" s="32"/>
       <c r="J93" s="33" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="26" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B94" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D94" s="29" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E94" s="28" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F94" s="28" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="G94" s="30" t="s">
         <v>93</v>
@@ -6664,27 +6861,27 @@
       </c>
       <c r="I94" s="32"/>
       <c r="J94" s="33" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="26" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B95" s="34" t="s">
         <v>70</v>
       </c>
       <c r="C95" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D95" s="29" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E95" s="28" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F95" s="28" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="G95" s="30" t="s">
         <v>93</v>
@@ -6694,30 +6891,30 @@
       </c>
       <c r="I95" s="32"/>
       <c r="J95" s="33" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="26" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B96" s="34" t="s">
         <v>70</v>
       </c>
       <c r="C96" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D96" s="29" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E96" s="28" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F96" s="28" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="G96" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H96" s="31" t="s">
         <v>61</v>
@@ -6727,25 +6924,25 @@
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="26" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B97" s="34" t="s">
         <v>70</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D97" s="29" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="E97" s="28" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F97" s="28" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="G97" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H97" s="31" t="s">
         <v>61</v>
@@ -6755,57 +6952,55 @@
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="26" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B98" s="34" t="s">
         <v>70</v>
       </c>
       <c r="C98" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D98" s="29" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E98" s="28" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="F98" s="28" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="G98" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H98" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="I98" s="32" t="n">
-        <v>46298</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="I98" s="32"/>
       <c r="J98" s="33" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="26" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B99" s="34" t="s">
         <v>70</v>
       </c>
       <c r="C99" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D99" s="29" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="E99" s="28" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F99" s="28" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="G99" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H99" s="31" t="s">
         <v>61</v>
@@ -6815,22 +7010,22 @@
     </row>
     <row r="100" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="26" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B100" s="34" t="s">
         <v>70</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D100" s="29" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E100" s="28" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F100" s="28" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="G100" s="30" t="s">
         <v>93</v>
@@ -6840,87 +7035,87 @@
       </c>
       <c r="I100" s="32"/>
       <c r="J100" s="33" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="26" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B101" s="34" t="s">
         <v>70</v>
       </c>
       <c r="C101" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D101" s="29" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="E101" s="28" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="F101" s="28" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="G101" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H101" s="31" t="s">
         <v>59</v>
       </c>
       <c r="I101" s="32"/>
       <c r="J101" s="33" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="26" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B102" s="34" t="s">
         <v>70</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D102" s="29" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="E102" s="28" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F102" s="28" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G102" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H102" s="31" t="s">
         <v>59</v>
       </c>
       <c r="I102" s="32"/>
       <c r="J102" s="33" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="26" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B103" s="36" t="s">
         <v>71</v>
       </c>
       <c r="C103" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D103" s="29" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E103" s="28" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F103" s="28" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="G103" s="30" t="s">
         <v>93</v>
@@ -6933,22 +7128,22 @@
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="26" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B104" s="36" t="s">
         <v>71</v>
       </c>
       <c r="C104" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D104" s="29" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E104" s="28" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="F104" s="28" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="G104" s="30" t="s">
         <v>93</v>
@@ -6961,25 +7156,25 @@
     </row>
     <row r="105" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="26" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B105" s="36" t="s">
         <v>71</v>
       </c>
       <c r="C105" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D105" s="29" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="F105" s="28" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="G105" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H105" s="31" t="s">
         <v>61</v>
@@ -6989,25 +7184,25 @@
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="26" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B106" s="36" t="s">
         <v>71</v>
       </c>
       <c r="C106" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D106" s="29" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E106" s="28" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="F106" s="28" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="G106" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H106" s="31" t="s">
         <v>61</v>
@@ -7017,22 +7212,22 @@
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="26" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B107" s="36" t="s">
         <v>71</v>
       </c>
       <c r="C107" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D107" s="29" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="E107" s="28" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="F107" s="28" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="G107" s="30" t="s">
         <v>93</v>
@@ -7045,22 +7240,22 @@
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="26" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B108" s="36" t="s">
         <v>71</v>
       </c>
       <c r="C108" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D108" s="29" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="E108" s="28" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="F108" s="28" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G108" s="30" t="s">
         <v>93</v>
@@ -7073,25 +7268,25 @@
     </row>
     <row r="109" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="26" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B109" s="36" t="s">
         <v>71</v>
       </c>
       <c r="C109" s="28" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D109" s="29" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="F109" s="28" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="G109" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H109" s="31" t="s">
         <v>61</v>
@@ -7101,25 +7296,25 @@
     </row>
     <row r="110" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="26" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B110" s="36" t="s">
         <v>71</v>
       </c>
       <c r="C110" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D110" s="29" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="F110" s="28" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="G110" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H110" s="31" t="s">
         <v>61</v>
@@ -7129,22 +7324,22 @@
     </row>
     <row r="111" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="26" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B111" s="36" t="s">
         <v>71</v>
       </c>
       <c r="C111" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D111" s="29" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E111" s="28" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="F111" s="28" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="G111" s="30" t="s">
         <v>93</v>
@@ -7157,25 +7352,25 @@
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="26" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B112" s="36" t="s">
         <v>71</v>
       </c>
       <c r="C112" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D112" s="29" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="E112" s="28" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F112" s="28" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="G112" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H112" s="31" t="s">
         <v>61</v>
@@ -7185,7 +7380,7 @@
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="26" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B113" s="39" t="s">
         <v>72</v>
@@ -7194,13 +7389,13 @@
         <v>89</v>
       </c>
       <c r="D113" s="29" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="E113" s="28" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="F113" s="28" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="G113" s="30" t="s">
         <v>93</v>
@@ -7213,7 +7408,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="26" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B114" s="39" t="s">
         <v>72</v>
@@ -7222,13 +7417,13 @@
         <v>89</v>
       </c>
       <c r="D114" s="29" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="E114" s="28" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="F114" s="28" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="G114" s="30" t="s">
         <v>93</v>
@@ -7241,7 +7436,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="26" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B115" s="39" t="s">
         <v>72</v>
@@ -7250,13 +7445,13 @@
         <v>89</v>
       </c>
       <c r="D115" s="29" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="F115" s="28" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="G115" s="30" t="s">
         <v>93</v>
@@ -7269,37 +7464,39 @@
     </row>
     <row r="116" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="26" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B116" s="39" t="s">
         <v>72</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D116" s="29" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E116" s="28" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="F116" s="28" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="G116" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H116" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I116" s="32"/>
+        <v>60</v>
+      </c>
+      <c r="I116" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J116" s="33" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="26" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B117" s="39" t="s">
         <v>72</v>
@@ -7308,13 +7505,13 @@
         <v>89</v>
       </c>
       <c r="D117" s="29" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="E117" s="28" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="F117" s="28" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="G117" s="30" t="s">
         <v>93</v>
@@ -7327,7 +7524,7 @@
     </row>
     <row r="118" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="26" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B118" s="27" t="s">
         <v>73</v>
@@ -7336,26 +7533,28 @@
         <v>89</v>
       </c>
       <c r="D118" s="29" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E118" s="28" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="F118" s="28" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="G118" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H118" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I118" s="32"/>
-      <c r="J118" s="33"/>
+      <c r="J118" s="33" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="26" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B119" s="27" t="s">
         <v>73</v>
@@ -7364,16 +7563,16 @@
         <v>89</v>
       </c>
       <c r="D119" s="29" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="E119" s="28" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="F119" s="28" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="G119" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H119" s="31" t="s">
         <v>61</v>
@@ -7383,7 +7582,7 @@
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="26" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="B120" s="27" t="s">
         <v>73</v>
@@ -7392,13 +7591,13 @@
         <v>89</v>
       </c>
       <c r="D120" s="29" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="E120" s="28" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="F120" s="28" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="G120" s="30" t="s">
         <v>93</v>
@@ -7408,12 +7607,12 @@
       </c>
       <c r="I120" s="32"/>
       <c r="J120" s="33" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="26" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="B121" s="27" t="s">
         <v>73</v>
@@ -7422,26 +7621,28 @@
         <v>89</v>
       </c>
       <c r="D121" s="29" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="E121" s="28" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="F121" s="28" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="G121" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H121" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I121" s="32"/>
-      <c r="J121" s="33"/>
+      <c r="J121" s="33" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="26" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B122" s="27" t="s">
         <v>73</v>
@@ -7450,13 +7651,13 @@
         <v>89</v>
       </c>
       <c r="D122" s="29" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="E122" s="28" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="F122" s="28" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="G122" s="30" t="s">
         <v>93</v>
@@ -7469,7 +7670,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="26" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="B123" s="27" t="s">
         <v>73</v>
@@ -7478,16 +7679,16 @@
         <v>89</v>
       </c>
       <c r="D123" s="29" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="E123" s="28" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="F123" s="28" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="G123" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H123" s="31" t="s">
         <v>61</v>
@@ -7497,7 +7698,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="26" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="B124" s="27" t="s">
         <v>73</v>
@@ -7506,41 +7707,43 @@
         <v>89</v>
       </c>
       <c r="D124" s="29" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="E124" s="28" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="F124" s="28" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="G124" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H124" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I124" s="32"/>
-      <c r="J124" s="33"/>
+      <c r="J124" s="33" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="26" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="B125" s="35" t="s">
         <v>74</v>
       </c>
       <c r="C125" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D125" s="29" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="E125" s="28" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="F125" s="28" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="G125" s="30" t="s">
         <v>93</v>
@@ -7553,25 +7756,25 @@
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="26" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="B126" s="35" t="s">
         <v>74</v>
       </c>
       <c r="C126" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D126" s="29" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="E126" s="28" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="F126" s="28" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="G126" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H126" s="31" t="s">
         <v>61</v>
@@ -7581,25 +7784,25 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="26" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="B127" s="35" t="s">
         <v>74</v>
       </c>
       <c r="C127" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D127" s="29" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="E127" s="28" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="F127" s="28" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="G127" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H127" s="31" t="s">
         <v>61</v>
@@ -7609,25 +7812,25 @@
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="26" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="B128" s="35" t="s">
         <v>74</v>
       </c>
       <c r="C128" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D128" s="29" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="E128" s="28" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="F128" s="28" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="G128" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H128" s="31" t="s">
         <v>61</v>
@@ -7637,25 +7840,25 @@
     </row>
     <row r="129" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="26" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="B129" s="35" t="s">
         <v>74</v>
       </c>
       <c r="C129" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D129" s="29" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="E129" s="28" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="F129" s="28" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="G129" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H129" s="31" t="s">
         <v>61</v>
@@ -7665,25 +7868,25 @@
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="26" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="B130" s="35" t="s">
         <v>74</v>
       </c>
       <c r="C130" s="28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D130" s="29" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="E130" s="28" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="F130" s="28" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="G130" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H130" s="31" t="s">
         <v>61</v>
@@ -7693,25 +7896,25 @@
     </row>
     <row r="131" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="26" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="B131" s="35" t="s">
         <v>74</v>
       </c>
       <c r="C131" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D131" s="29" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="E131" s="28" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="F131" s="28" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="G131" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H131" s="31" t="s">
         <v>61</v>
@@ -7721,7 +7924,7 @@
     </row>
     <row r="132" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="26" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="B132" s="37" t="s">
         <v>75</v>
@@ -7730,13 +7933,13 @@
         <v>89</v>
       </c>
       <c r="D132" s="29" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="E132" s="28" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="F132" s="28" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="G132" s="30" t="s">
         <v>93</v>
@@ -7749,7 +7952,7 @@
     </row>
     <row r="133" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="26" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="B133" s="37" t="s">
         <v>75</v>
@@ -7758,13 +7961,13 @@
         <v>89</v>
       </c>
       <c r="D133" s="29" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="E133" s="28" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="F133" s="28" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="G133" s="30" t="s">
         <v>93</v>
@@ -7774,12 +7977,12 @@
       </c>
       <c r="I133" s="32"/>
       <c r="J133" s="33" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="26" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="B134" s="37" t="s">
         <v>75</v>
@@ -7788,56 +7991,58 @@
         <v>89</v>
       </c>
       <c r="D134" s="29" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="E134" s="28" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="F134" s="28" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="G134" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H134" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I134" s="32"/>
-      <c r="J134" s="33"/>
+      <c r="J134" s="33" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="26" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="B135" s="37" t="s">
         <v>75</v>
       </c>
       <c r="C135" s="28" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D135" s="29" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="E135" s="28" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="F135" s="28" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="G135" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H135" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I135" s="32"/>
       <c r="J135" s="33" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="26" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="B136" s="37" t="s">
         <v>75</v>
@@ -7846,54 +8051,58 @@
         <v>89</v>
       </c>
       <c r="D136" s="29" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="E136" s="28" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="F136" s="28" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="G136" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H136" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I136" s="32"/>
-      <c r="J136" s="33"/>
+      <c r="J136" s="33" t="s">
+        <v>700</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="26" t="s">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="B137" s="37" t="s">
         <v>75</v>
       </c>
       <c r="C137" s="28" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D137" s="29" t="s">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="E137" s="28" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="F137" s="28" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="G137" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H137" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I137" s="32"/>
-      <c r="J137" s="33"/>
+      <c r="J137" s="33" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="26" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="B138" s="37" t="s">
         <v>75</v>
@@ -7902,26 +8111,28 @@
         <v>89</v>
       </c>
       <c r="D138" s="29" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="E138" s="28" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="F138" s="28" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="G138" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H138" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I138" s="32"/>
-      <c r="J138" s="33"/>
+      <c r="J138" s="33" t="s">
+        <v>710</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="26" t="s">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="B139" s="37" t="s">
         <v>75</v>
@@ -7930,82 +8141,88 @@
         <v>89</v>
       </c>
       <c r="D139" s="29" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="E139" s="28" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="F139" s="28" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="G139" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H139" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I139" s="32"/>
-      <c r="J139" s="33"/>
+      <c r="J139" s="33" t="s">
+        <v>710</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="26" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="B140" s="37" t="s">
         <v>75</v>
       </c>
       <c r="C140" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D140" s="29" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="E140" s="28" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="F140" s="28" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="G140" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H140" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I140" s="32"/>
-      <c r="J140" s="33"/>
+      <c r="J140" s="33" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="26" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="B141" s="37" t="s">
         <v>75</v>
       </c>
       <c r="C141" s="28" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="D141" s="29" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="E141" s="28" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="G141" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H141" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I141" s="32"/>
-      <c r="J141" s="33"/>
+      <c r="J141" s="33" t="s">
+        <v>725</v>
+      </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="26" t="s">
-        <v>713</v>
+        <v>726</v>
       </c>
       <c r="B142" s="37" t="s">
         <v>75</v>
@@ -8014,26 +8231,28 @@
         <v>89</v>
       </c>
       <c r="D142" s="29" t="s">
-        <v>714</v>
+        <v>727</v>
       </c>
       <c r="E142" s="28" t="s">
-        <v>715</v>
+        <v>728</v>
       </c>
       <c r="F142" s="28" t="s">
-        <v>716</v>
+        <v>729</v>
       </c>
       <c r="G142" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H142" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I142" s="32"/>
-      <c r="J142" s="33"/>
+      <c r="J142" s="33" t="s">
+        <v>730</v>
+      </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="26" t="s">
-        <v>717</v>
+        <v>731</v>
       </c>
       <c r="B143" s="37" t="s">
         <v>75</v>
@@ -8042,25 +8261,231 @@
         <v>89</v>
       </c>
       <c r="D143" s="29" t="s">
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="E143" s="28" t="s">
-        <v>719</v>
+        <v>733</v>
       </c>
       <c r="F143" s="28" t="s">
-        <v>720</v>
+        <v>734</v>
       </c>
       <c r="G143" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H143" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I143" s="32"/>
-      <c r="J143" s="33"/>
+      <c r="J143" s="33" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="26" t="s">
+        <v>736</v>
+      </c>
+      <c r="B144" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C144" s="28" t="s">
+        <v>737</v>
+      </c>
+      <c r="D144" s="29" t="s">
+        <v>738</v>
+      </c>
+      <c r="E144" s="28" t="s">
+        <v>739</v>
+      </c>
+      <c r="F144" s="28" t="s">
+        <v>740</v>
+      </c>
+      <c r="G144" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="H144" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="I144" s="32"/>
+      <c r="J144" s="33" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="26" t="s">
+        <v>742</v>
+      </c>
+      <c r="B145" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C145" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D145" s="29" t="s">
+        <v>743</v>
+      </c>
+      <c r="E145" s="28" t="s">
+        <v>744</v>
+      </c>
+      <c r="F145" s="28" t="s">
+        <v>745</v>
+      </c>
+      <c r="G145" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="H145" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="I145" s="32"/>
+      <c r="J145" s="33" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="26" t="s">
+        <v>747</v>
+      </c>
+      <c r="B146" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C146" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D146" s="29" t="s">
+        <v>748</v>
+      </c>
+      <c r="E146" s="28" t="s">
+        <v>749</v>
+      </c>
+      <c r="F146" s="28" t="s">
+        <v>750</v>
+      </c>
+      <c r="G146" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="H146" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="I146" s="32"/>
+      <c r="J146" s="33" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="26" t="s">
+        <v>752</v>
+      </c>
+      <c r="B147" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C147" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D147" s="29" t="s">
+        <v>753</v>
+      </c>
+      <c r="E147" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="F147" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="G147" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="H147" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="I147" s="32"/>
+      <c r="J147" s="33" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="26" t="s">
+        <v>736</v>
+      </c>
+      <c r="B148" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C148" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D148" s="29" t="s">
+        <v>757</v>
+      </c>
+      <c r="E148" s="28" t="s">
+        <v>758</v>
+      </c>
+      <c r="F148" s="28" t="s">
+        <v>759</v>
+      </c>
+      <c r="G148" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="H148" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="I148" s="32"/>
+      <c r="J148" s="33"/>
+    </row>
+    <row r="149" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="26" t="s">
+        <v>742</v>
+      </c>
+      <c r="B149" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C149" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D149" s="29" t="s">
+        <v>760</v>
+      </c>
+      <c r="E149" s="28" t="s">
+        <v>761</v>
+      </c>
+      <c r="F149" s="28" t="s">
+        <v>762</v>
+      </c>
+      <c r="G149" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="H149" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="I149" s="32"/>
+      <c r="J149" s="33"/>
+    </row>
+    <row r="150" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="26" t="s">
+        <v>747</v>
+      </c>
+      <c r="B150" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C150" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D150" s="29" t="s">
+        <v>763</v>
+      </c>
+      <c r="E150" s="28" t="s">
+        <v>764</v>
+      </c>
+      <c r="F150" s="28" t="s">
+        <v>765</v>
+      </c>
+      <c r="G150" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="H150" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="I150" s="32"/>
+      <c r="J150" s="33"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J143"/>
+  <autoFilter ref="A1:J150"/>
   <conditionalFormatting sqref="H2:H300">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"Đạt"</formula>
@@ -8071,12 +8496,12 @@
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"Chờ thử lại"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>"Bỏ qua"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G300">
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>"Cao"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/rehearsal/checklist.xlsx
+++ b/docs/rehearsal/checklist.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Checklist!$1:$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Checklist!$A$1:$J$150</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Checklist!$A$1:$J$147</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,12 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="761">
   <si>
     <t xml:space="preserve">StayGuard: checklist diễn tập (Gate 1)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cập nhật 03/10/2026 khoảng 11:40 theo kết quả diễn tập và báo cáo của các phiên (142 case; thêm TT-19 đến TT-29, CA-10, CA-11, LO-10, DP-09, DN-13, DN-14, TD-06 đến TD-08). Chưa có chỉnh sửa tay của Khai. Bổ sung sau 11:40 cùng ngày: kết quả các phiên API-1, API-2, WEB-1, WEB-2 và QA tự động, hai ảnh Nhật ký và Giao dịch của Khai. Chỉ TT-25 đánh Đạt (ảnh của Khai); các dòng Lỗi từ QA tự động ghi rõ 'chưa thử tay'. Từ chiều 03/10: mục tiêu là bản demo cho portfolio, không có khách hàng thật. Các dòng cần SePay thật, ngân hàng thật, máy chủ thật hoặc nghiệp vụ khách hàng đã chuyển Bỏ qua kèm lý do. Thêm GL-13 đến GL-16 cho bản demo. Phạm vi mới (03/10): demo portfolio, không có khách thật. Các mục cần nhà nghỉ thật, tiền thật hoặc hạ tầng thật chuyển sang Bỏ qua kèm lý do; thêm GL-13 đến GL-15 cho phần đóng gói demo.</t>
+    <t xml:space="preserve">Cập nhật 03/10/2026 tối. Phạm vi: demo portfolio, không có khách thật; các dòng cần nhà nghỉ thật, tiền thật hoặc hạ tầng thật là Bỏ qua kèm lý do. Kết quả tự động (QA, make demo-check) ghi Đạt kèm ghi chú 'QA tự động &lt;ngày&gt;'; các dòng cần mắt người (GD-03 đến GD-07, TD-05, TD-08) chỉ nhận ghi chú và chờ bạn xem. TT-21, TT-22, TT-26 giữ Chờ thử lại vì test chưa phủ hết kỳ vọng. Đã gộp GL-13 đến GL-16 của phiên khác; các dòng trùng mã đã gỡ.</t>
   </si>
   <si>
     <t xml:space="preserve">Cách dùng</t>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Trạng thái</t>
   </si>
   <si>
-    <t xml:space="preserve">Chưa làm, Đạt, Lỗi, Chờ thử lại (đã sửa trong code, cần thử lại sau khi rebuild), Bỏ qua (ghi lý do ở Ghi chú). Chỉ đánh Đạt khi chính bạn đã thấy kết quả.</t>
+    <t xml:space="preserve">Chưa làm, Đạt, Lỗi, Chờ thử lại (đã sửa trong code, cần thử lại sau khi rebuild), Bỏ qua (ghi lý do ở Ghi chú). Đạt khi bạn tự thấy kết quả, hoặc khi test tự động đạt (ghi 'QA tự động &lt;ngày&gt;' ở Ghi chú). Dòng cần mắt người chỉ Đạt khi bạn xem.</t>
   </si>
   <si>
     <t xml:space="preserve">Thêm test case mới</t>
@@ -561,7 +561,8 @@
     <t xml:space="preserve">Màn không có quyền. Không có nút Gán.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thử ở đúng tab đang đăng nhập. Mở tab mới thì bị đưa về đăng nhập (sessionStorage mỗi tab): xem DN-07 và DN-13.</t>
+    <t xml:space="preserve">Thử ở đúng tab đang đăng nhập. Mở tab mới thì bị đưa về đăng nhập (sessionStorage mỗi tab): xem DN-07 và DN-13.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-06</t>
@@ -574,6 +575,9 @@
   </si>
   <si>
     <t xml:space="preserve">Không còn nút gán, hoặc bị từ chối vì đã gán.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-07</t>
@@ -605,7 +609,8 @@
   </si>
   <si>
     <t xml:space="preserve">QA tự động + đọc code (chưa thử tay): biên lai chỉ có một dòng chuyển khoản cộng dồn vì ListReceiptPayments chỉ lấy thanh toán PAID; dòng chuyển thiếu vẫn là MISMATCH trong Cần xử lý sau khi phiếu đã thanh toán. Giao API-2.
-QA tự động: biên lai chỉ có một dòng chuyển khoản cộng dồn, không phải hai; khoản chuyển thiếu vẫn nằm ở Cần xử lý sau khi phiếu đã trả. Đọc code: ListReceiptPayments chỉ lấy thanh toán PAID, mỗi thanh toán một dòng. Giao API-2.</t>
+QA tự động: biên lai chỉ có một dòng chuyển khoản cộng dồn, không phải hai; khoản chuyển thiếu vẫn nằm ở Cần xử lý sau khi phiếu đã trả. Đọc code: ListReceiptPayments chỉ lấy thanh toán PAID, mỗi thanh toán một dòng. Giao API-2.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-09</t>
@@ -649,7 +654,8 @@
     <t xml:space="preserve">Hiện nút Tiền ra đang bị xám vì webhook chỉ nghe Tiền vào.
 QA tự động + đọc code, chưa thử tay: tiền ra được lưu thành 'Chưa rõ phiếu' và gán được vào phiếu (InsertPaymentEvent luôn ghi UNMATCHED). Giao API-2 (kết quả IGNORED).
 Đã sửa (API-2 2b9b88f: tiền ra ghi IGNORED, không hiện, không gán được). QA tự động đạt trên bản build mới. Dòng đã lưu trước migration 0031 không phân loại được lại.
-Đã sửa (API-2 2b9b88f / API-1 185a589, b7aa449 / WEB-2 e174d33, 695a060). QA tự động đạt trên bản mới. Thử lại sau rebuild.</t>
+Đã sửa (API-2 2b9b88f / API-1 185a589, b7aa449 / WEB-2 e174d33, 695a060). QA tự động đạt trên bản mới. Thử lại sau rebuild.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-12</t>
@@ -702,6 +708,9 @@
   </si>
   <si>
     <t xml:space="preserve">Màn tự hiện QR hết hạn, có nút tạo QR mới. Tiền chuyển vào mã cũ vẫn được ghi nhận khi SePay báo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA tự động 03/10/2026. QR không bao giờ chuyển EXPIRED theo thời gian: ExpirePending chỉ chạy khi tạo thanh toán mới, qrExpiryMinutes chỉ được lưu. Đề xuất: suy ra EXPIRED lúc đọc, giữ bản ghi PENDING để tiền về mã cũ vẫn khớp. Giao API-2.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-16</t>
@@ -736,7 +745,8 @@
   <si>
     <t xml:space="preserve">Tùy chọn.
 Đã sửa (API-2 2b9b88f: tiền vào tài khoản lạ ghi IGNORED). QA báo lỗi nhưng bài test so với mọi dòng Chưa rõ phiếu cùng số tiền trong nhà nghỉ dùng chung; QA sửa test (số tiền riêng, so số dòng trước và sau).
-Đã sửa (API-2 2b9b88f). Test QA bị lỗi: so khớp theo số tiền và vướng các dòng UNMATCHED do spec khác để lại; QA đổi sang số tiền riêng.</t>
+Đã sửa (API-2 2b9b88f). Test QA bị lỗi: so khớp theo số tiền và vướng các dòng UNMATCHED do spec khác để lại; QA đổi sang số tiền riêng.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-18</t>
@@ -764,7 +774,8 @@
   </si>
   <si>
     <t xml:space="preserve">03/10 08:43: ô phòng đã ghi Chờ thanh toán nhưng khung chi tiết ghi Phòng đang bảo trì (A101, A103). Nguyên nhân: nhánh mặc định của khung chi tiết. API-2 đã đẩy pendingPayment; WEB-1 chưa xong nút tiếp tục.
-Đã sửa (WEB-1 4c8c1a2): ô Chờ thanh toán, khung có tổng, đã nhận, còn thiếu, Tiếp tục thanh toán, Thu tiền mặt, không có Trả phòng. Chủ và lễ tân, phone và desktop; e2e đạt trên API thật. Thử lại sau rebuild.</t>
+Đã sửa (WEB-1 4c8c1a2): ô Chờ thanh toán, khung có tổng, đã nhận, còn thiếu, Tiếp tục thanh toán, Thu tiền mặt, không có Trả phòng. Chủ và lễ tân, phone và desktop; e2e đạt trên API thật. Thử lại sau rebuild.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-20</t>
@@ -795,7 +806,8 @@
   </si>
   <si>
     <t xml:space="preserve">03/10 08:48: A102 bị kẹt, ô phòng mất loại thuê và giờ ở, không bấm vào được.
-Đã sửa một phần (WEB-1 f6add89): ô Chờ hoàn ₫X và nút Hoàn lại khách khi mở lại. Mới có unit test, chưa chạy với hoàn cọc thật. Thử lại sau rebuild.</t>
+Đã sửa một phần (WEB-1 f6add89): ô Chờ hoàn ₫X và nút Hoàn lại khách khi mở lại. Mới có unit test, chưa chạy với hoàn cọc thật. Thử lại sau rebuild.
+QA tự động đạt. Giữ Chờ thử lại vì kỳ vọng có 'dữ liệu cũ cũng xử lý được', test dùng nhà nghỉ mới.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-22</t>
@@ -811,7 +823,8 @@
   </si>
   <si>
     <t xml:space="preserve">API-2 phải trả lời: giờ ra chốt lúc mở màn hay lúc xác nhận thanh toán.
-WEB-1 báo API chốt giờ ra lúc xác nhận thanh toán (rời màn mà chưa xác nhận thì lượt vẫn đang ở). Cần xác nhận lại với API-2 rồi thử tay.</t>
+WEB-1 báo API chốt giờ ra lúc xác nhận thanh toán (rời màn mà chưa xác nhận thì lượt vẫn đang ở). Cần xác nhận lại với API-2 rồi thử tay.
+QA tự động đạt. Giữ Chờ thử lại cho tới khi API-2 xác nhận quy tắc giờ ra (WEB-1 báo: chốt lúc xác nhận thanh toán).</t>
   </si>
   <si>
     <t xml:space="preserve">TT-23</t>
@@ -827,7 +840,8 @@
   </si>
   <si>
     <t xml:space="preserve">03/10 A103: sau khi tải lại, khung chi tiết quay về màn chọn cách thanh toán.
-Đã sửa (WEB-1 f6add89): mở lại phòng đã trả sẽ tiếp tục đúng thanh toán cũ, nút QR dùng lại thanh toán đang có. e2e đạt. Thử lại sau rebuild.</t>
+Đã sửa (WEB-1 f6add89): mở lại phòng đã trả sẽ tiếp tục đúng thanh toán cũ, nút QR dùng lại thanh toán đang có. e2e đạt. Thử lại sau rebuild.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-24</t>
@@ -842,7 +856,8 @@
     <t xml:space="preserve">Tóm tắt chỉ đọc: Đã trả phòng lúc, trạng thái thanh toán, hóa đơn. Không có Trả phòng, Thêm dịch vụ, Sửa giờ, Chuyển phòng. API từ chối các thao tác đó (409).</t>
   </si>
   <si>
-    <t xml:space="preserve">03/10 10:16: A103 hiện Đã ở 0 giờ và nút Trả phòng. API-2 (409 STAY_NOT_ACTIVE) và WEB-1 (dc15ef9) đã sửa.</t>
+    <t xml:space="preserve">03/10 10:16: A103 hiện Đã ở 0 giờ và nút Trả phòng. API-2 (409 STAY_NOT_ACTIVE) và WEB-1 (dc15ef9) đã sửa.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-25</t>
@@ -873,7 +888,8 @@
     <t xml:space="preserve">Dòng Đã cọc bằng đúng cọc, Phải thu = tổng trừ cọc trừ tiền đã nhận.</t>
   </si>
   <si>
-    <t xml:space="preserve">03/10 08:42: A101 ghi cọc 0đ, phải thu 80.000đ. API-2 đối chiếu cọc lúc đọc và sửa dữ liệu cũ; WEB-1 đọc đúng trường. Gốc rễ chưa tái hiện được.</t>
+    <t xml:space="preserve">03/10 08:42: A101 ghi cọc 0đ, phải thu 80.000đ. API-2 đối chiếu cọc lúc đọc và sửa dữ liệu cũ; WEB-1 đọc đúng trường. Gốc rễ chưa tái hiện được.
+QA tự động đạt trên nhà nghỉ mới. Gốc rễ ban đầu chưa tái hiện được nên giữ Chờ thử lại cho tới khi bạn mở lại màn trả phòng trên dữ liệu của bạn.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-27</t>
@@ -888,7 +904,8 @@
     <t xml:space="preserve">Hiện "Chờ hoàn 20.000đ cho khách" (REFUND_PENDING), không phải "Còn 20.000đ chưa thu".</t>
   </si>
   <si>
-    <t xml:space="preserve">03/10 A101, A102 ghi "Còn 20.000đ chưa thu". API-2 đã thêm REFUND_PENDING và đổi cảnh báo cũ; WEB-2 đã đọc.</t>
+    <t xml:space="preserve">03/10 A101, A102 ghi "Còn 20.000đ chưa thu". API-2 đã thêm REFUND_PENDING và đổi cảnh báo cũ; WEB-2 đã đọc.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-28</t>
@@ -926,7 +943,8 @@
   </si>
   <si>
     <t xml:space="preserve">A101 ghi "Còn thiếu 0đ" trong khi màn trả phòng ghi phải thu 80.000đ. Đã giao WEB-1 quy tắc nhãn ô phòng.
-Đã sửa (WEB-1 f6add89): Còn thiếu ₫X, Chờ hoàn ₫X hoặc Cần kiểm tra phiếu, không còn Còn thiếu 0đ. Unit test đạt vi và en. Thử lại sau rebuild.</t>
+Đã sửa (WEB-1 f6add89): Còn thiếu ₫X, Chờ hoàn ₫X hoặc Cần kiểm tra phiếu, không còn Còn thiếu 0đ. Unit test đạt vi và en. Thử lại sau rebuild.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">CA-01</t>
@@ -980,7 +998,8 @@
     <t xml:space="preserve">Hiện Thiếu 70.000đ. Nút Kết ca khóa tới khi có lý do. Chủ nhận cảnh báo thiếu tiền. Đối soát ca hiện chênh lệch.</t>
   </si>
   <si>
-    <t xml:space="preserve">Mới thấy màn: Thiếu 340.000đ, nút Kết ca khóa tới khi nhập lý do (10:12). Chưa bấm kết ca. Số 340.000đ lệch Tổng quan 320.000đ: xem CA-10.</t>
+    <t xml:space="preserve">Mới thấy màn: Thiếu 340.000đ, nút Kết ca khóa tới khi nhập lý do (10:12). Chưa bấm kết ca. Số 340.000đ lệch Tổng quan 320.000đ: xem CA-10.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">CA-05</t>
@@ -1016,10 +1035,11 @@
     <t xml:space="preserve">Chủ nhận phòng và trả phòng, thu tiền mặt</t>
   </si>
   <si>
-    <t xml:space="preserve">Giao dịch ghi Tiền mặt, không gắn ca, vẫn tính vào doanh thu. Không có nút Kết ca hay Chi tiền.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theo quy tắc 17a: nếu lễ tân có ca mở ở tòa đó thì khoản chủ thu hoặc hoàn tiền mặt tính vào ca đó, đánh dấu do chủ; chỉ khi không có ca mở mới không gắn ca. Xem CA-10.</t>
+    <t xml:space="preserve">Chủ thu tiền mặt khi lễ tân có ca mở ở tòa đó: khoản ghi vào ca mở gần nhất có quyền ở tòa đó, đánh dấu do chủ. Không có ca mở: ghi là Tiền mặt của chủ, không gắn ca, vẫn tính vào doanh thu. Không có nút Kết ca hay Chi tiền.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theo quy tắc 17a: nếu lễ tân có ca mở ở tòa đó thì khoản chủ thu hoặc hoàn tiền mặt tính vào ca đó, đánh dấu do chủ; chỉ khi không có ca mở mới không gắn ca. Xem CA-10.
+QA tự động 03/10/2026. Theo quy tắc 17a; cột Kết quả mong đợi đã cập nhật.</t>
   </si>
   <si>
     <t xml:space="preserve">CA-08</t>
@@ -1034,6 +1054,9 @@
     <t xml:space="preserve">Thấy số đếm, khoản chi, lý do, người bàn giao.</t>
   </si>
   <si>
+    <t xml:space="preserve">QA tự động 03/10/2026. Màn đối soát ca không nêu người bàn giao. Đề xuất: người đóng ca (tên, vai trò) và quỹ để lại; hệ thống không có người nhận ca. Giao API-2 và WEB-2.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA-09</t>
   </si>
   <si>
@@ -1061,7 +1084,8 @@
     <t xml:space="preserve">Hai con số bằng nhau. Khoản chủ làm nằm trong ca đang mở và có nhãn do chủ.</t>
   </si>
   <si>
-    <t xml:space="preserve">03/10 10:16: Kết ca 340.000đ, Tổng quan 320.000đ. API-2 xác nhận nguyên nhân (chủ hoàn tiền mặt không gắn ca) và sửa; quy tắc 17a đã chấp nhận.</t>
+    <t xml:space="preserve">03/10 10:16: Kết ca 340.000đ, Tổng quan 320.000đ. API-2 xác nhận nguyên nhân (chủ hoàn tiền mặt không gắn ca) và sửa; quy tắc 17a đã chấp nhận.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">CA-11</t>
@@ -1077,7 +1101,8 @@
   </si>
   <si>
     <t xml:space="preserve">API-2 đang thêm danh sách movements; WEB-1 làm màn sau đó.
-Đã làm (API-2 movements, WEB-1 a391f43): mỗi dòng mở ra giờ, phòng, loại, số tiền có dấu, nhãn do chủ. Thử lại sau rebuild.</t>
+Đã làm (API-2 movements, WEB-1 a391f43): mỗi dòng mở ra giờ, phòng, loại, số tiền có dấu, nhãn do chủ. Thử lại sau rebuild.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">LO-01</t>
@@ -1208,7 +1233,8 @@
     <t xml:space="preserve">Chỉ nhận 9–11 chữ số, đầu 0 hoặc +84, có thông báo lỗi rõ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã có unit test (phone.test.ts), chưa có e2e.</t>
+    <t xml:space="preserve">Đã có unit test (phone.test.ts), chưa có e2e.
+Server cũng chặn SĐT sai (d480325). QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">DP-01</t>
@@ -1332,7 +1358,8 @@
   </si>
   <si>
     <t xml:space="preserve">03/10 10:04: khung trên sơ đồ chỉ có nút Dọn xong; trang /clean có đủ. Đã giao WEB-1 dùng một component chung.
-Đã sửa (WEB-1 25fc4cb): khung trên sơ đồ dùng cùng một component với /clean, đủ 4 hành động; người chỉ có quyền Xem không thấy hành động. Thử lại sau rebuild.</t>
+Đã sửa (WEB-1 25fc4cb): khung trên sơ đồ dùng cùng một component với /clean, đủ 4 hành động; người chỉ có quyền Xem không thấy hành động. Thử lại sau rebuild.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">GT-01</t>
@@ -1373,7 +1400,8 @@
   <si>
     <t xml:space="preserve">QA GI-02 + đọc code, chưa thử tay: nhật ký xem CCCD có ghi nhưng xếp nhóm Giá và cài đặt, lọc Giấy tờ khách không ra. Cả 8 mã GUEST_ID_* và 2 mã INSTALLER_* bị sai nhóm (tiền tố chữ hoa). Giao API-1.
 Đã sửa (API-1 185a589): mọi mã GUEST_ID_* và INSTALLER_* nằm đúng nhóm; thêm test duyệt mọi mã thao tác.
-Đã sửa (API-2 2b9b88f / API-1 185a589, b7aa449 / WEB-2 e174d33, 695a060). QA tự động đạt trên bản mới. Thử lại sau rebuild.</t>
+Đã sửa (API-2 2b9b88f / API-1 185a589, b7aa449 / WEB-2 e174d33, 695a060). QA tự động đạt trên bản mới. Thử lại sau rebuild.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">GT-04</t>
@@ -1439,7 +1467,8 @@
     <t xml:space="preserve">Không thấy số hay dữ liệu ảnh trong log.</t>
   </si>
   <si>
-    <t xml:space="preserve">Chỉ dùng số CCCD thử, không dùng số thật.</t>
+    <t xml:space="preserve">Chỉ dùng số CCCD thử, không dùng số thật.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">GT-09</t>
@@ -1536,7 +1565,8 @@
   </si>
   <si>
     <t xml:space="preserve">Mở /vi/owner/transactions ở tab mới bị đưa về đăng nhập, không thấy màn không có quyền. Nghi do sessionStorage mỗi tab; đã giao cookie phiên (DN-13). Thử lại ở cùng tab.
-Đã sửa (WEB-1 cbf7c96 cookie phiên, f6add89 chặn trang chủ theo vai trò). Thử lại ở tab mới sau rebuild; nhớ đăng nhập lại.</t>
+Đã sửa (WEB-1 cbf7c96 cookie phiên, f6add89 chặn trang chủ theo vai trò). Thử lại ở tab mới sau rebuild; nhớ đăng nhập lại.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">DN-08</t>
@@ -1609,7 +1639,8 @@
   </si>
   <si>
     <t xml:space="preserve">API đã có cookie phiên (d818ebd). WEB-1 chưa làm phần web.
-Đã sửa (WEB-1 cbf7c96): cookie sg_session, tab thứ hai mở /vi/clean?room=… vẫn đăng nhập; e2e đạt. Thử lại sau rebuild, đăng nhập lại.</t>
+Đã sửa (WEB-1 cbf7c96): cookie sg_session, tab thứ hai mở /vi/clean?room=… vẫn đăng nhập; e2e đạt. Thử lại sau rebuild, đăng nhập lại.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">DN-14</t>
@@ -1625,7 +1656,8 @@
   </si>
   <si>
     <t xml:space="preserve">Chờ cookie phiên (DN-13) để thử trong cùng một phiên.
-Đã sửa (WEB-1 f6add89): màn không có quyền kèm nút về sơ đồ phòng, giữ phiên; chỉ 401 mới về đăng nhập kèm đường dẫn quay lại. e2e đạt. Thử lại sau rebuild.</t>
+Đã sửa (WEB-1 f6add89): màn không có quyền kèm nút về sơ đồ phòng, giữ phiên; chỉ 401 mới về đăng nhập kèm đường dẫn quay lại. e2e đạt. Thử lại sau rebuild.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TD-01</t>
@@ -1640,7 +1672,8 @@
     <t xml:space="preserve">Doanh thu bằng tổng hóa đơn đã thanh toán ở mọi chỗ. Số phòng theo tòa khớp sơ đồ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Doanh thu 580.000đ khớp 7 lượt. Tiền mặt phải có lệch (Kết ca 340.000đ, Tổng quan 320.000đ); API-2 đã sửa bằng một sổ tiền mặt chung (quy tắc 17a). Thử lại sau rebuild.</t>
+    <t xml:space="preserve">Doanh thu 580.000đ khớp 7 lượt. Tiền mặt phải có lệch (Kết ca 340.000đ, Tổng quan 320.000đ); API-2 đã sửa bằng một sổ tiền mặt chung (quy tắc 17a). Thử lại sau rebuild.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TD-02</t>
@@ -1681,7 +1714,8 @@
   <si>
     <t xml:space="preserve">Ảnh Nhật ký 03/10: dòng 'Thanh toán xong {room}', 'Tạo thanh toán {room}', 'Trả phòng {room}', 'Nhận phòng {room}' hiện nguyên {room}; cột Người trống ở dòng 10:12 (thao tác của hệ thống). Nguyên nhân: API không ghi số phòng vào nhật ký; thêm 27 mã thao tác chưa có câu mô tả (đọc code). Giao API-1 (room, bill) và WEB-2 (câu mô tả).
 Đã sửa (API-1 b7aa449 điền room, bill; WEB-2 e174d33, 695a060 mô tả đủ 57 thao tác, người trống hiện Hệ thống). QA UI-01 đạt ở /owner/activity.
-Đã sửa (API-2 2b9b88f / API-1 185a589, b7aa449 / WEB-2 e174d33, 695a060). QA tự động đạt trên bản mới. Thử lại sau rebuild.</t>
+Đã sửa (API-2 2b9b88f / API-1 185a589, b7aa449 / WEB-2 e174d33, 695a060). QA tự động đạt trên bản mới. Thử lại sau rebuild.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TD-05</t>
@@ -1696,6 +1730,9 @@
     <t xml:space="preserve">Không có Kết ca hay Chi tiền. Có thanh chọn tòa.</t>
   </si>
   <si>
+    <t xml:space="preserve">QA tự động 03/10/2026. Test đạt; cần bạn xem bằng mắt trước khi đánh Đạt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TD-06</t>
   </si>
   <si>
@@ -1709,7 +1746,8 @@
   </si>
   <si>
     <t xml:space="preserve">03/10: Cần xử lý ngay ghi 8 mục, còn khoản 100.000đ đã gán và các phiếu đã thanh toán. API-2 đã thêm resolvedAt; chờ WEB-2.
-Đã sửa (WEB-2 5aaa0f2): Cần xử lý chỉ đếm việc còn mở, việc xong hiện mờ kèm Đã giải quyết lúc. Đạt trên API thật ở stack của lane. Thử lại sau rebuild.</t>
+Đã sửa (WEB-2 5aaa0f2): Cần xử lý chỉ đếm việc còn mở, việc xong hiện mờ kèm Đã giải quyết lúc. Đạt trên API thật ở stack của lane. Thử lại sau rebuild.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TD-07</t>
@@ -1724,7 +1762,8 @@
     <t xml:space="preserve">Mở dòng thời gian lượt ở của chủ, không mở trang của lễ tân.</t>
   </si>
   <si>
-    <t xml:space="preserve">WEB-2 đã đẩy (a36d2bf): Xem trên cảnh báo có lượt ở mở /owner/stay. Cần thử lại sau rebuild.</t>
+    <t xml:space="preserve">WEB-2 đã đẩy (a36d2bf): Xem trên cảnh báo có lượt ở mở /owner/stay. Cần thử lại sau rebuild.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">TD-08</t>
@@ -1739,7 +1778,8 @@
     <t xml:space="preserve">Câu dễ đọc có giờ, không hiện chuỗi 2026-10-02T18:01:20Z.</t>
   </si>
   <si>
-    <t xml:space="preserve">WEB-2 đã đẩy: SEPAY_UPDATED hiện câu đọc được thay cho chuỗi ISO. Cần thử lại sau rebuild.</t>
+    <t xml:space="preserve">WEB-2 đã đẩy: SEPAY_UPDATED hiện câu đọc được thay cho chuỗi ISO. Cần thử lại sau rebuild.
+QA tự động 03/10/2026. Test đạt; cần bạn xem bằng mắt trước khi đánh Đạt.</t>
   </si>
   <si>
     <t xml:space="preserve">CD-01</t>
@@ -1975,7 +2015,8 @@
     <t xml:space="preserve">Báo key fingerprint mismatch, không lộ khóa. Trả khóa cũ thì chạy lại.</t>
   </si>
   <si>
-    <t xml:space="preserve">Không làm trên môi trường có dữ liệu thật.</t>
+    <t xml:space="preserve">Không làm trên môi trường có dữ liệu thật.
+QA tự động 03/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">VH-04</t>
@@ -2371,36 +2412,8 @@
     <t xml:space="preserve">README có mô tả sản phẩm, sơ đồ kiến trúc (Go, PostgreSQL RLS, Next.js nhúng vào binary), lệnh chạy demo, ảnh các màn chính, video hoặc GIF 3 phút, và các quyết định kỹ thuật nổi bật (tiền số nguyên, webhook ký HMAC, idempotency, RLS, nhật ký không sửa được).</t>
   </si>
   <si>
-    <t xml:space="preserve">Dùng lại script chụp ảnh của QA và quay video bằng Playwright.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">README, ảnh chụp màn hình và kịch bản demo 3 phút</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) README: mô tả sản phẩm, kiến trúc, cách chạy local
-2) Ảnh chụp 6 đến 8 màn chính (vi) và một GIF luồng thanh toán
-3) Kịch bản demo: các bước và vai trò</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Người lạ chạy được app trong 10 phút theo README. Có ảnh, GIF và kịch bản. Ghi rõ dữ liệu là giả.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đặt lại dữ liệu demo bằng một lệnh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chạy lệnh đặt lại dữ liệu demo, mở app, chọn từng vai trò</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Có đủ phòng, lượt ở, giao dịch mẫu để xem ngay. Chạy lại lệnh thì về đúng trạng thái đó.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luồng SePay test mode quay thành video ngắn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chạy tunnel, tạo giao dịch mô phỏng ở SePay test mode, quay màn lễ tân và chủ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Video 1 đến 2 phút: QR, tiền về qua webhook, phiếu Đã thanh toán, chuyển thiếu rồi bù. Không lộ khóa, mã hook hay số tài khoản.</t>
+    <t xml:space="preserve">Dùng lại script chụp ảnh của QA và quay video bằng Playwright.
+Có thể gồm video luồng SePay test mode (quay ở buổi thử tay); không lộ khóa, mã hook hay số tài khoản.</t>
   </si>
 </sst>
 </file>
@@ -3584,7 +3597,7 @@
       </c>
       <c r="C6" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A6,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D6" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A6,Checklist!$H$2:$H$300,"Lỗi")</f>
@@ -3592,7 +3605,7 @@
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A6,Checklist!$H$2:$H$300,"Chờ thử lại")</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F6" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A6,Checklist!$H$2:$H$300,"Bỏ qua")</f>
@@ -3600,11 +3613,11 @@
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">B6-C6-D6-E6-F6</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">IFERROR(C6/(B6-F6),0)</f>
-        <v>0.296296296296296</v>
+        <v>0.851851851851852</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3617,15 +3630,15 @@
       </c>
       <c r="C7" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A7,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D7" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A7,Checklist!$H$2:$H$300,"Lỗi")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A7,Checklist!$H$2:$H$300,"Chờ thử lại")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A7,Checklist!$H$2:$H$300,"Bỏ qua")</f>
@@ -3633,11 +3646,11 @@
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">B7-C7-D7-E7-F7</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H7" s="10" t="n">
         <f aca="false">IFERROR(C7/(B7-F7),0)</f>
-        <v>0.0909090909090909</v>
+        <v>0.909090909090909</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3650,7 +3663,7 @@
       </c>
       <c r="C8" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A8,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D8" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A8,Checklist!$H$2:$H$300,"Lỗi")</f>
@@ -3666,11 +3679,11 @@
       </c>
       <c r="G8" s="9" t="n">
         <f aca="false">B8-C8-D8-E8-F8</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H8" s="10" t="n">
         <f aca="false">IFERROR(C8/(B8-F8),0)</f>
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3683,7 +3696,7 @@
       </c>
       <c r="C9" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A9,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D9" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A9,Checklist!$H$2:$H$300,"Lỗi")</f>
@@ -3691,7 +3704,7 @@
       </c>
       <c r="E9" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A9,Checklist!$H$2:$H$300,"Chờ thử lại")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A9,Checklist!$H$2:$H$300,"Bỏ qua")</f>
@@ -3699,11 +3712,11 @@
       </c>
       <c r="G9" s="9" t="n">
         <f aca="false">B9-C9-D9-E9-F9</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H9" s="10" t="n">
         <f aca="false">IFERROR(C9/(B9-F9),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3716,7 +3729,7 @@
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A10,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A10,Checklist!$H$2:$H$300,"Lỗi")</f>
@@ -3724,7 +3737,7 @@
       </c>
       <c r="E10" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A10,Checklist!$H$2:$H$300,"Chờ thử lại")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A10,Checklist!$H$2:$H$300,"Bỏ qua")</f>
@@ -3732,11 +3745,11 @@
       </c>
       <c r="G10" s="9" t="n">
         <f aca="false">B10-C10-D10-E10-F10</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H10" s="10" t="n">
         <f aca="false">IFERROR(C10/(B10-F10),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3749,7 +3762,7 @@
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A11,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A11,Checklist!$H$2:$H$300,"Lỗi")</f>
@@ -3757,7 +3770,7 @@
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A11,Checklist!$H$2:$H$300,"Chờ thử lại")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A11,Checklist!$H$2:$H$300,"Bỏ qua")</f>
@@ -3765,11 +3778,11 @@
       </c>
       <c r="G11" s="9" t="n">
         <f aca="false">B11-C11-D11-E11-F11</f>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H11" s="10" t="n">
         <f aca="false">IFERROR(C11/(B11-F11),0)</f>
-        <v>0</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3782,7 +3795,7 @@
       </c>
       <c r="C12" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A12,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D12" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A12,Checklist!$H$2:$H$300,"Lỗi")</f>
@@ -3790,7 +3803,7 @@
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A12,Checklist!$H$2:$H$300,"Chờ thử lại")</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F12" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A12,Checklist!$H$2:$H$300,"Bỏ qua")</f>
@@ -3798,11 +3811,11 @@
       </c>
       <c r="G12" s="9" t="n">
         <f aca="false">B12-C12-D12-E12-F12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" s="10" t="n">
         <f aca="false">IFERROR(C12/(B12-F12),0)</f>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3815,7 +3828,7 @@
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A13,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A13,Checklist!$H$2:$H$300,"Lỗi")</f>
@@ -3831,11 +3844,11 @@
       </c>
       <c r="G13" s="9" t="n">
         <f aca="false">B13-C13-D13-E13-F13</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H13" s="10" t="n">
         <f aca="false">IFERROR(C13/(B13-F13),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3848,7 +3861,7 @@
       </c>
       <c r="C14" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A14,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A14,Checklist!$H$2:$H$300,"Lỗi")</f>
@@ -3864,11 +3877,11 @@
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">B14-C14-D14-E14-F14</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H14" s="10" t="n">
         <f aca="false">IFERROR(C14/(B14-F14),0)</f>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3881,7 +3894,7 @@
       </c>
       <c r="C15" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A15,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D15" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A15,Checklist!$H$2:$H$300,"Lỗi")</f>
@@ -3897,11 +3910,11 @@
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">B15-C15-D15-E15-F15</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H15" s="10" t="n">
         <f aca="false">IFERROR(C15/(B15-F15),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3943,7 +3956,7 @@
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$300,$A17)</f>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C17" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A17,Checklist!$H$2:$H$300,"Đạt")</f>
@@ -3963,7 +3976,7 @@
       </c>
       <c r="G17" s="9" t="n">
         <f aca="false">B17-C17-D17-E17-F17</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H17" s="10" t="n">
         <f aca="false">IFERROR(C17/(B17-F17),0)</f>
@@ -3976,19 +3989,19 @@
       </c>
       <c r="B18" s="18" t="n">
         <f aca="false">SUM(B5:B17)</f>
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">SUM(C5:C17)</f>
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="D18" s="18" t="n">
         <f aca="false">SUM(D5:D17)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="18" t="n">
         <f aca="false">SUM(E5:E17)</f>
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">SUM(F5:F17)</f>
@@ -3996,11 +4009,11 @@
       </c>
       <c r="G18" s="18" t="n">
         <f aca="false">SUM(G5:G17)</f>
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">IFERROR(C18/(B18-F18),0)</f>
-        <v>0.130769230769231</v>
+        <v>0.795275590551181</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4014,7 +4027,7 @@
       </c>
       <c r="B21" s="21" t="n">
         <f aca="false">COUNTIFS(Checklist!$G$2:$G$300,"Cao")-COUNTIFS(Checklist!$G$2:$G$300,"Cao",Checklist!$H$2:$H$300,"Đạt")-COUNTIFS(Checklist!$G$2:$G$300,"Cao",Checklist!$H$2:$H$300,"Bỏ qua")</f>
-        <v>67</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4023,7 +4036,7 @@
       </c>
       <c r="B22" s="21" t="n">
         <f aca="false">D18</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4619,9 +4632,11 @@
         <v>93</v>
       </c>
       <c r="H17" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I17" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I17" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J17" s="33" t="s">
         <v>173</v>
       </c>
@@ -4649,14 +4664,18 @@
         <v>93</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I18" s="32"/>
-      <c r="J18" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I18" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J18" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B19" s="34" t="s">
         <v>64</v>
@@ -4665,58 +4684,62 @@
         <v>147</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G19" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I19" s="32"/>
-      <c r="J19" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I19" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J19" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G20" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H20" s="31" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="I20" s="32" t="n">
         <v>46298</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>64</v>
@@ -4725,26 +4748,30 @@
         <v>141</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G21" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I21" s="32"/>
-      <c r="J21" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I21" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J21" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>64</v>
@@ -4753,84 +4780,94 @@
         <v>147</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G22" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I22" s="32"/>
-      <c r="J22" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I22" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J22" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G23" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I23" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I23" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J23" s="33" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B24" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G24" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I24" s="32"/>
-      <c r="J24" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I24" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J24" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B25" s="34" t="s">
         <v>64</v>
@@ -4839,13 +4876,13 @@
         <v>169</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G25" s="30" t="s">
         <v>93</v>
@@ -4857,12 +4894,12 @@
         <v>46298</v>
       </c>
       <c r="J25" s="33" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B26" s="34" t="s">
         <v>64</v>
@@ -4871,13 +4908,13 @@
         <v>169</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G26" s="30" t="s">
         <v>93</v>
@@ -4889,12 +4926,12 @@
         <v>46298</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B27" s="34" t="s">
         <v>64</v>
@@ -4906,23 +4943,27 @@
         <v>40</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G27" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I27" s="32"/>
-      <c r="J27" s="33"/>
+        <v>58</v>
+      </c>
+      <c r="I27" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J27" s="33" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B28" s="34" t="s">
         <v>64</v>
@@ -4931,13 +4972,13 @@
         <v>169</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G28" s="30" t="s">
         <v>134</v>
@@ -4947,42 +4988,44 @@
       </c>
       <c r="I28" s="32"/>
       <c r="J28" s="33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="26" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B29" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G29" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I29" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I29" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J29" s="33" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B30" s="34" t="s">
         <v>64</v>
@@ -4991,26 +5034,30 @@
         <v>169</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G30" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I30" s="32"/>
-      <c r="J30" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I30" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J30" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="26" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B31" s="34" t="s">
         <v>64</v>
@@ -5019,28 +5066,30 @@
         <v>169</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G31" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I31" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I31" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J31" s="33" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="26" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B32" s="34" t="s">
         <v>64</v>
@@ -5049,13 +5098,13 @@
         <v>141</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G32" s="30" t="s">
         <v>93</v>
@@ -5067,12 +5116,12 @@
         <v>46298</v>
       </c>
       <c r="J32" s="33" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B33" s="34" t="s">
         <v>64</v>
@@ -5081,13 +5130,13 @@
         <v>169</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G33" s="30" t="s">
         <v>93</v>
@@ -5097,12 +5146,12 @@
       </c>
       <c r="I33" s="32"/>
       <c r="J33" s="33" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="26" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B34" s="34" t="s">
         <v>64</v>
@@ -5111,13 +5160,13 @@
         <v>169</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G34" s="30" t="s">
         <v>93</v>
@@ -5127,12 +5176,12 @@
       </c>
       <c r="I34" s="32"/>
       <c r="J34" s="33" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B35" s="34" t="s">
         <v>64</v>
@@ -5141,28 +5190,30 @@
         <v>169</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G35" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H35" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I35" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I35" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J35" s="33" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B36" s="34" t="s">
         <v>64</v>
@@ -5171,28 +5222,30 @@
         <v>130</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G36" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H36" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I36" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I36" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J36" s="33" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="26" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B37" s="34" t="s">
         <v>64</v>
@@ -5201,13 +5254,13 @@
         <v>141</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G37" s="30" t="s">
         <v>134</v>
@@ -5219,12 +5272,12 @@
         <v>46298</v>
       </c>
       <c r="J37" s="33" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="26" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B38" s="34" t="s">
         <v>64</v>
@@ -5233,13 +5286,13 @@
         <v>169</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G38" s="30" t="s">
         <v>93</v>
@@ -5249,12 +5302,12 @@
       </c>
       <c r="I38" s="32"/>
       <c r="J38" s="33" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="26" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B39" s="34" t="s">
         <v>64</v>
@@ -5263,43 +5316,45 @@
         <v>141</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G39" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H39" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I39" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I39" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J39" s="33" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B40" s="34" t="s">
         <v>64</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G40" s="30" t="s">
         <v>93</v>
@@ -5309,12 +5364,12 @@
       </c>
       <c r="I40" s="32"/>
       <c r="J40" s="33" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B41" s="34" t="s">
         <v>64</v>
@@ -5323,28 +5378,30 @@
         <v>169</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G41" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I41" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I41" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J41" s="33" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B42" s="35" t="s">
         <v>65</v>
@@ -5353,13 +5410,13 @@
         <v>169</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G42" s="30" t="s">
         <v>93</v>
@@ -5371,12 +5428,12 @@
         <v>46298</v>
       </c>
       <c r="J42" s="33" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B43" s="35" t="s">
         <v>65</v>
@@ -5385,26 +5442,30 @@
         <v>169</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G43" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I43" s="32"/>
-      <c r="J43" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I43" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J43" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B44" s="35" t="s">
         <v>65</v>
@@ -5413,26 +5474,30 @@
         <v>169</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F44" s="28" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G44" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I44" s="32"/>
-      <c r="J44" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I44" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J44" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B45" s="35" t="s">
         <v>65</v>
@@ -5441,28 +5506,30 @@
         <v>130</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E45" s="28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F45" s="28" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G45" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H45" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I45" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I45" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J45" s="33" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="26" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B46" s="35" t="s">
         <v>65</v>
@@ -5471,26 +5538,30 @@
         <v>169</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G46" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H46" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I46" s="32"/>
-      <c r="J46" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I46" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J46" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B47" s="35" t="s">
         <v>65</v>
@@ -5499,26 +5570,30 @@
         <v>169</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G47" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I47" s="32"/>
-      <c r="J47" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I47" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J47" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="26" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B48" s="35" t="s">
         <v>65</v>
@@ -5527,28 +5602,30 @@
         <v>141</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F48" s="28" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G48" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H48" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I48" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I48" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J48" s="33" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="26" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B49" s="35" t="s">
         <v>65</v>
@@ -5557,26 +5634,30 @@
         <v>141</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E49" s="28" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F49" s="28" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G49" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H49" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I49" s="32"/>
-      <c r="J49" s="33"/>
+        <v>58</v>
+      </c>
+      <c r="I49" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J49" s="33" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B50" s="35" t="s">
         <v>65</v>
@@ -5585,56 +5666,62 @@
         <v>141</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F50" s="28" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G50" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H50" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I50" s="32"/>
-      <c r="J50" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I50" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J50" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B51" s="35" t="s">
         <v>65</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F51" s="28" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G51" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H51" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I51" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I51" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J51" s="33" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B52" s="35" t="s">
         <v>65</v>
@@ -5643,28 +5730,30 @@
         <v>169</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E52" s="28" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F52" s="28" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G52" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H52" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I52" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I52" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J52" s="33" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="26" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B53" s="36" t="s">
         <v>66</v>
@@ -5673,13 +5762,13 @@
         <v>169</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F53" s="28" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G53" s="30" t="s">
         <v>93</v>
@@ -5691,12 +5780,12 @@
         <v>46298</v>
       </c>
       <c r="J53" s="33" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="26" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B54" s="36" t="s">
         <v>66</v>
@@ -5705,26 +5794,30 @@
         <v>169</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E54" s="28" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F54" s="28" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G54" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H54" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I54" s="32"/>
-      <c r="J54" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I54" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J54" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B55" s="36" t="s">
         <v>66</v>
@@ -5736,23 +5829,27 @@
         <v>46</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F55" s="28" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="G55" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H55" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I55" s="32"/>
-      <c r="J55" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I55" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J55" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="26" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B56" s="36" t="s">
         <v>66</v>
@@ -5761,26 +5858,30 @@
         <v>169</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E56" s="28" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F56" s="28" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="G56" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H56" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I56" s="32"/>
-      <c r="J56" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I56" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J56" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="26" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B57" s="36" t="s">
         <v>66</v>
@@ -5789,26 +5890,30 @@
         <v>169</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F57" s="28" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G57" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H57" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I57" s="32"/>
-      <c r="J57" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I57" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J57" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="26" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B58" s="36" t="s">
         <v>66</v>
@@ -5817,13 +5922,13 @@
         <v>169</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F58" s="28" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G58" s="30" t="s">
         <v>134</v>
@@ -5833,12 +5938,12 @@
       </c>
       <c r="I58" s="32"/>
       <c r="J58" s="33" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="26" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B59" s="36" t="s">
         <v>66</v>
@@ -5847,13 +5952,13 @@
         <v>169</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F59" s="28" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G59" s="30" t="s">
         <v>134</v>
@@ -5865,12 +5970,12 @@
         <v>46298</v>
       </c>
       <c r="J59" s="33" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="26" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B60" s="36" t="s">
         <v>66</v>
@@ -5879,26 +5984,30 @@
         <v>141</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F60" s="28" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G60" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H60" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I60" s="32"/>
-      <c r="J60" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I60" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J60" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="26" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B61" s="36" t="s">
         <v>66</v>
@@ -5907,26 +6016,30 @@
         <v>169</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F61" s="28" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G61" s="30" t="s">
         <v>145</v>
       </c>
       <c r="H61" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I61" s="32"/>
-      <c r="J61" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I61" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J61" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="26" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B62" s="36" t="s">
         <v>66</v>
@@ -5935,13 +6048,13 @@
         <v>169</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F62" s="28" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G62" s="30" t="s">
         <v>134</v>
@@ -5953,12 +6066,12 @@
         <v>46298</v>
       </c>
       <c r="J62" s="33" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="26" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B63" s="37" t="s">
         <v>67</v>
@@ -5967,110 +6080,126 @@
         <v>169</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F63" s="28" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G63" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H63" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I63" s="32"/>
-      <c r="J63" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I63" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J63" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="26" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B64" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E64" s="28" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F64" s="28" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G64" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H64" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I64" s="32"/>
-      <c r="J64" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I64" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J64" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="26" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B65" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F65" s="28" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G65" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H65" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I65" s="32"/>
-      <c r="J65" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I65" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J65" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="26" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B66" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F66" s="28" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G66" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H66" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I66" s="32"/>
-      <c r="J66" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I66" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J66" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="26" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B67" s="37" t="s">
         <v>67</v>
@@ -6079,26 +6208,30 @@
         <v>169</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E67" s="28" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F67" s="28" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="G67" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H67" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I67" s="32"/>
-      <c r="J67" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I67" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J67" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="26" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B68" s="37" t="s">
         <v>67</v>
@@ -6107,112 +6240,126 @@
         <v>141</v>
       </c>
       <c r="D68" s="29" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F68" s="28" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G68" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H68" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I68" s="32"/>
-      <c r="J68" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I68" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J68" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="26" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B69" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E69" s="28" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F69" s="28" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="G69" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H69" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I69" s="32"/>
-      <c r="J69" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I69" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J69" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="26" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B70" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C70" s="28" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F70" s="28" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G70" s="30" t="s">
         <v>145</v>
       </c>
       <c r="H70" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I70" s="32"/>
-      <c r="J70" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I70" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J70" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="26" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B71" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D71" s="29" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E71" s="28" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F71" s="28" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G71" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H71" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I71" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I71" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J71" s="33" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="26" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B72" s="38" t="s">
         <v>68</v>
@@ -6221,26 +6368,30 @@
         <v>169</v>
       </c>
       <c r="D72" s="29" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F72" s="28" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="G72" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H72" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I72" s="32"/>
-      <c r="J72" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I72" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J72" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="26" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B73" s="38" t="s">
         <v>68</v>
@@ -6249,26 +6400,30 @@
         <v>169</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F73" s="28" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="G73" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H73" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I73" s="32"/>
-      <c r="J73" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I73" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J73" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="26" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B74" s="38" t="s">
         <v>68</v>
@@ -6277,28 +6432,30 @@
         <v>141</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E74" s="28" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F74" s="28" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="G74" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H74" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I74" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I74" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J74" s="33" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="26" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B75" s="38" t="s">
         <v>68</v>
@@ -6307,54 +6464,62 @@
         <v>141</v>
       </c>
       <c r="D75" s="29" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E75" s="28" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F75" s="28" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="G75" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H75" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I75" s="32"/>
-      <c r="J75" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I75" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J75" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="26" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B76" s="38" t="s">
         <v>68</v>
       </c>
       <c r="C76" s="28" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F76" s="28" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G76" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H76" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I76" s="32"/>
-      <c r="J76" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I76" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J76" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="26" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B77" s="38" t="s">
         <v>68</v>
@@ -6363,26 +6528,30 @@
         <v>130</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E77" s="28" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F77" s="28" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G77" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H77" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I77" s="32"/>
-      <c r="J77" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I77" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J77" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="26" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B78" s="38" t="s">
         <v>68</v>
@@ -6391,26 +6560,30 @@
         <v>169</v>
       </c>
       <c r="D78" s="29" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E78" s="28" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F78" s="28" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="G78" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H78" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I78" s="32"/>
-      <c r="J78" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I78" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J78" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="26" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B79" s="38" t="s">
         <v>68</v>
@@ -6419,28 +6592,30 @@
         <v>89</v>
       </c>
       <c r="D79" s="29" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E79" s="28" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F79" s="28" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G79" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H79" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I79" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I79" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J79" s="33" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="26" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B80" s="38" t="s">
         <v>68</v>
@@ -6449,26 +6624,30 @@
         <v>89</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E80" s="28" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F80" s="28" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="G80" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H80" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I80" s="32"/>
-      <c r="J80" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I80" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J80" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="26" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B81" s="39" t="s">
         <v>69</v>
@@ -6477,26 +6656,30 @@
         <v>169</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E81" s="28" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="G81" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H81" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I81" s="32"/>
-      <c r="J81" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I81" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J81" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="26" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B82" s="39" t="s">
         <v>69</v>
@@ -6505,26 +6688,30 @@
         <v>169</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F82" s="28" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="G82" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H82" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I82" s="32"/>
-      <c r="J82" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I82" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J82" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="26" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B83" s="39" t="s">
         <v>69</v>
@@ -6533,26 +6720,30 @@
         <v>169</v>
       </c>
       <c r="D83" s="29" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E83" s="28" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F83" s="28" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="G83" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H83" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I83" s="32"/>
-      <c r="J83" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I83" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J83" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="26" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B84" s="39" t="s">
         <v>69</v>
@@ -6561,13 +6752,13 @@
         <v>141</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E84" s="28" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F84" s="28" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="G84" s="30" t="s">
         <v>93</v>
@@ -6580,63 +6771,71 @@
     </row>
     <row r="85" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="26" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B85" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C85" s="28" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E85" s="28" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F85" s="28" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="G85" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H85" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I85" s="32"/>
-      <c r="J85" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I85" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J85" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="26" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B86" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C86" s="28" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F86" s="28" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G86" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H86" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I86" s="32"/>
-      <c r="J86" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I86" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J86" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="26" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B87" s="39" t="s">
         <v>69</v>
@@ -6645,84 +6844,94 @@
         <v>169</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E87" s="28" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F87" s="28" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G87" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H87" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I87" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I87" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J87" s="33" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="26" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B88" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C88" s="28" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E88" s="28" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F88" s="28" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G88" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H88" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I88" s="32"/>
-      <c r="J88" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I88" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J88" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="26" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B89" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E89" s="28" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F89" s="28" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G89" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H89" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I89" s="32"/>
-      <c r="J89" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I89" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J89" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="26" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B90" s="39" t="s">
         <v>69</v>
@@ -6731,26 +6940,30 @@
         <v>141</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E90" s="28" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F90" s="28" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="G90" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H90" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I90" s="32"/>
-      <c r="J90" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I90" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J90" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="26" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B91" s="39" t="s">
         <v>69</v>
@@ -6759,26 +6972,30 @@
         <v>169</v>
       </c>
       <c r="D91" s="29" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E91" s="28" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F91" s="28" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="G91" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H91" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I91" s="32"/>
-      <c r="J91" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I91" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J91" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="26" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B92" s="39" t="s">
         <v>69</v>
@@ -6787,26 +7004,30 @@
         <v>141</v>
       </c>
       <c r="D92" s="29" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E92" s="28" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F92" s="28" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G92" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H92" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I92" s="32"/>
-      <c r="J92" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I92" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J92" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="26" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B93" s="39" t="s">
         <v>69</v>
@@ -6815,28 +7036,30 @@
         <v>169</v>
       </c>
       <c r="D93" s="29" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E93" s="28" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F93" s="28" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G93" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H93" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I93" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I93" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J93" s="33" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="26" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B94" s="39" t="s">
         <v>69</v>
@@ -6845,28 +7068,30 @@
         <v>169</v>
       </c>
       <c r="D94" s="29" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E94" s="28" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F94" s="28" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="G94" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H94" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I94" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I94" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J94" s="33" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="26" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B95" s="34" t="s">
         <v>70</v>
@@ -6875,28 +7100,30 @@
         <v>141</v>
       </c>
       <c r="D95" s="29" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E95" s="28" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F95" s="28" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="G95" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H95" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I95" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I95" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J95" s="33" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="26" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B96" s="34" t="s">
         <v>70</v>
@@ -6905,26 +7132,30 @@
         <v>141</v>
       </c>
       <c r="D96" s="29" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E96" s="28" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F96" s="28" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G96" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H96" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I96" s="32"/>
-      <c r="J96" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I96" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J96" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="26" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B97" s="34" t="s">
         <v>70</v>
@@ -6933,26 +7164,30 @@
         <v>141</v>
       </c>
       <c r="D97" s="29" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E97" s="28" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F97" s="28" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="G97" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H97" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I97" s="32"/>
-      <c r="J97" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I97" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J97" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="26" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B98" s="34" t="s">
         <v>70</v>
@@ -6961,28 +7196,30 @@
         <v>141</v>
       </c>
       <c r="D98" s="29" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E98" s="28" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F98" s="28" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="G98" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H98" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I98" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I98" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J98" s="33" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="26" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B99" s="34" t="s">
         <v>70</v>
@@ -6991,13 +7228,13 @@
         <v>141</v>
       </c>
       <c r="D99" s="29" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E99" s="28" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F99" s="28" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="G99" s="30" t="s">
         <v>145</v>
@@ -7006,11 +7243,13 @@
         <v>61</v>
       </c>
       <c r="I99" s="32"/>
-      <c r="J99" s="33"/>
+      <c r="J99" s="33" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="26" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B100" s="34" t="s">
         <v>70</v>
@@ -7019,28 +7258,30 @@
         <v>141</v>
       </c>
       <c r="D100" s="29" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E100" s="28" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F100" s="28" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="G100" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H100" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I100" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I100" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J100" s="33" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="26" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B101" s="34" t="s">
         <v>70</v>
@@ -7049,28 +7290,30 @@
         <v>141</v>
       </c>
       <c r="D101" s="29" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E101" s="28" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F101" s="28" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="G101" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H101" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I101" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I101" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J101" s="33" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="26" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B102" s="34" t="s">
         <v>70</v>
@@ -7079,13 +7322,13 @@
         <v>141</v>
       </c>
       <c r="D102" s="29" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="E102" s="28" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F102" s="28" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="G102" s="30" t="s">
         <v>145</v>
@@ -7095,12 +7338,12 @@
       </c>
       <c r="I102" s="32"/>
       <c r="J102" s="33" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="26" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B103" s="36" t="s">
         <v>71</v>
@@ -7109,26 +7352,30 @@
         <v>141</v>
       </c>
       <c r="D103" s="29" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E103" s="28" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="F103" s="28" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="G103" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H103" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I103" s="32"/>
-      <c r="J103" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I103" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J103" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="26" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B104" s="36" t="s">
         <v>71</v>
@@ -7137,26 +7384,30 @@
         <v>141</v>
       </c>
       <c r="D104" s="29" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="E104" s="28" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="F104" s="28" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="G104" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H104" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I104" s="32"/>
-      <c r="J104" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I104" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J104" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="26" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B105" s="36" t="s">
         <v>71</v>
@@ -7165,26 +7416,30 @@
         <v>141</v>
       </c>
       <c r="D105" s="29" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="F105" s="28" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="G105" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H105" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I105" s="32"/>
-      <c r="J105" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I105" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J105" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="26" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B106" s="36" t="s">
         <v>71</v>
@@ -7193,26 +7448,30 @@
         <v>141</v>
       </c>
       <c r="D106" s="29" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="E106" s="28" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="F106" s="28" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="G106" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H106" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I106" s="32"/>
-      <c r="J106" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I106" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J106" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="26" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B107" s="36" t="s">
         <v>71</v>
@@ -7221,26 +7480,30 @@
         <v>141</v>
       </c>
       <c r="D107" s="29" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="E107" s="28" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="F107" s="28" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G107" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H107" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I107" s="32"/>
-      <c r="J107" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I107" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J107" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="26" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B108" s="36" t="s">
         <v>71</v>
@@ -7249,54 +7512,62 @@
         <v>141</v>
       </c>
       <c r="D108" s="29" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="E108" s="28" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="F108" s="28" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="G108" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H108" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I108" s="32"/>
-      <c r="J108" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I108" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J108" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="26" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B109" s="36" t="s">
         <v>71</v>
       </c>
       <c r="C109" s="28" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D109" s="29" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="F109" s="28" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="G109" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H109" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I109" s="32"/>
-      <c r="J109" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I109" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J109" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="26" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B110" s="36" t="s">
         <v>71</v>
@@ -7305,26 +7576,30 @@
         <v>141</v>
       </c>
       <c r="D110" s="29" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="F110" s="28" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="G110" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H110" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I110" s="32"/>
-      <c r="J110" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I110" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J110" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="26" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B111" s="36" t="s">
         <v>71</v>
@@ -7333,26 +7608,30 @@
         <v>141</v>
       </c>
       <c r="D111" s="29" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="E111" s="28" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F111" s="28" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="G111" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H111" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I111" s="32"/>
-      <c r="J111" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I111" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J111" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="26" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B112" s="36" t="s">
         <v>71</v>
@@ -7361,26 +7640,30 @@
         <v>141</v>
       </c>
       <c r="D112" s="29" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="E112" s="28" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="F112" s="28" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="G112" s="30" t="s">
         <v>145</v>
       </c>
       <c r="H112" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I112" s="32"/>
-      <c r="J112" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I112" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J112" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="26" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B113" s="39" t="s">
         <v>72</v>
@@ -7389,26 +7672,30 @@
         <v>89</v>
       </c>
       <c r="D113" s="29" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="E113" s="28" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="F113" s="28" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="G113" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H113" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I113" s="32"/>
-      <c r="J113" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I113" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J113" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="26" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B114" s="39" t="s">
         <v>72</v>
@@ -7417,26 +7704,30 @@
         <v>89</v>
       </c>
       <c r="D114" s="29" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="E114" s="28" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="F114" s="28" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="G114" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H114" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I114" s="32"/>
-      <c r="J114" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I114" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J114" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="26" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B115" s="39" t="s">
         <v>72</v>
@@ -7445,41 +7736,45 @@
         <v>89</v>
       </c>
       <c r="D115" s="29" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="F115" s="28" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="G115" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H115" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I115" s="32"/>
-      <c r="J115" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I115" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J115" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="26" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B116" s="39" t="s">
         <v>72</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D116" s="29" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="E116" s="28" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="F116" s="28" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="G116" s="30" t="s">
         <v>134</v>
@@ -7491,12 +7786,12 @@
         <v>46298</v>
       </c>
       <c r="J116" s="33" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="26" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B117" s="39" t="s">
         <v>72</v>
@@ -7505,13 +7800,13 @@
         <v>89</v>
       </c>
       <c r="D117" s="29" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E117" s="28" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="F117" s="28" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="G117" s="30" t="s">
         <v>93</v>
@@ -7524,7 +7819,7 @@
     </row>
     <row r="118" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="26" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B118" s="27" t="s">
         <v>73</v>
@@ -7533,13 +7828,13 @@
         <v>89</v>
       </c>
       <c r="D118" s="29" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="E118" s="28" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="F118" s="28" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="G118" s="30" t="s">
         <v>93</v>
@@ -7549,12 +7844,12 @@
       </c>
       <c r="I118" s="32"/>
       <c r="J118" s="33" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="26" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B119" s="27" t="s">
         <v>73</v>
@@ -7563,26 +7858,30 @@
         <v>89</v>
       </c>
       <c r="D119" s="29" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E119" s="28" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F119" s="28" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="G119" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H119" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I119" s="32"/>
-      <c r="J119" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I119" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J119" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="26" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B120" s="27" t="s">
         <v>73</v>
@@ -7591,28 +7890,30 @@
         <v>89</v>
       </c>
       <c r="D120" s="29" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E120" s="28" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="F120" s="28" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="G120" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H120" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I120" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I120" s="32" t="n">
+        <v>46298</v>
+      </c>
       <c r="J120" s="33" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="26" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B121" s="27" t="s">
         <v>73</v>
@@ -7621,13 +7922,13 @@
         <v>89</v>
       </c>
       <c r="D121" s="29" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E121" s="28" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="F121" s="28" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="G121" s="30" t="s">
         <v>93</v>
@@ -7637,12 +7938,12 @@
       </c>
       <c r="I121" s="32"/>
       <c r="J121" s="33" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="26" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B122" s="27" t="s">
         <v>73</v>
@@ -7651,26 +7952,30 @@
         <v>89</v>
       </c>
       <c r="D122" s="29" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E122" s="28" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="F122" s="28" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G122" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H122" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I122" s="32"/>
-      <c r="J122" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I122" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J122" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="26" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B123" s="27" t="s">
         <v>73</v>
@@ -7679,26 +7984,30 @@
         <v>89</v>
       </c>
       <c r="D123" s="29" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="E123" s="28" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="F123" s="28" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G123" s="30" t="s">
         <v>134</v>
       </c>
       <c r="H123" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I123" s="32"/>
-      <c r="J123" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I123" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="J123" s="33" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="26" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B124" s="27" t="s">
         <v>73</v>
@@ -7707,13 +8016,13 @@
         <v>89</v>
       </c>
       <c r="D124" s="29" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E124" s="28" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="F124" s="28" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="G124" s="30" t="s">
         <v>145</v>
@@ -7723,12 +8032,12 @@
       </c>
       <c r="I124" s="32"/>
       <c r="J124" s="33" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="26" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B125" s="35" t="s">
         <v>74</v>
@@ -7737,13 +8046,13 @@
         <v>169</v>
       </c>
       <c r="D125" s="29" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E125" s="28" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="F125" s="28" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="G125" s="30" t="s">
         <v>93</v>
@@ -7756,7 +8065,7 @@
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="26" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B126" s="35" t="s">
         <v>74</v>
@@ -7765,13 +8074,13 @@
         <v>141</v>
       </c>
       <c r="D126" s="29" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E126" s="28" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="F126" s="28" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="G126" s="30" t="s">
         <v>134</v>
@@ -7784,7 +8093,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="26" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B127" s="35" t="s">
         <v>74</v>
@@ -7793,13 +8102,13 @@
         <v>141</v>
       </c>
       <c r="D127" s="29" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="E127" s="28" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="F127" s="28" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="G127" s="30" t="s">
         <v>134</v>
@@ -7808,11 +8117,13 @@
         <v>61</v>
       </c>
       <c r="I127" s="32"/>
-      <c r="J127" s="33"/>
+      <c r="J127" s="33" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="26" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B128" s="35" t="s">
         <v>74</v>
@@ -7821,13 +8132,13 @@
         <v>141</v>
       </c>
       <c r="D128" s="29" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="E128" s="28" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="F128" s="28" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G128" s="30" t="s">
         <v>134</v>
@@ -7836,11 +8147,13 @@
         <v>61</v>
       </c>
       <c r="I128" s="32"/>
-      <c r="J128" s="33"/>
+      <c r="J128" s="33" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="26" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B129" s="35" t="s">
         <v>74</v>
@@ -7849,13 +8162,13 @@
         <v>169</v>
       </c>
       <c r="D129" s="29" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E129" s="28" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="F129" s="28" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G129" s="30" t="s">
         <v>134</v>
@@ -7864,11 +8177,13 @@
         <v>61</v>
       </c>
       <c r="I129" s="32"/>
-      <c r="J129" s="33"/>
+      <c r="J129" s="33" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="26" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B130" s="35" t="s">
         <v>74</v>
@@ -7877,13 +8192,13 @@
         <v>130</v>
       </c>
       <c r="D130" s="29" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E130" s="28" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="F130" s="28" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G130" s="30" t="s">
         <v>134</v>
@@ -7892,11 +8207,13 @@
         <v>61</v>
       </c>
       <c r="I130" s="32"/>
-      <c r="J130" s="33"/>
+      <c r="J130" s="33" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="26" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B131" s="35" t="s">
         <v>74</v>
@@ -7905,13 +8222,13 @@
         <v>169</v>
       </c>
       <c r="D131" s="29" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E131" s="28" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="F131" s="28" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="G131" s="30" t="s">
         <v>145</v>
@@ -7920,11 +8237,13 @@
         <v>61</v>
       </c>
       <c r="I131" s="32"/>
-      <c r="J131" s="33"/>
+      <c r="J131" s="33" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="26" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B132" s="37" t="s">
         <v>75</v>
@@ -7933,13 +8252,13 @@
         <v>89</v>
       </c>
       <c r="D132" s="29" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E132" s="28" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="F132" s="28" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="G132" s="30" t="s">
         <v>93</v>
@@ -7952,7 +8271,7 @@
     </row>
     <row r="133" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="26" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B133" s="37" t="s">
         <v>75</v>
@@ -7961,13 +8280,13 @@
         <v>89</v>
       </c>
       <c r="D133" s="29" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E133" s="28" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="F133" s="28" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G133" s="30" t="s">
         <v>93</v>
@@ -7977,12 +8296,12 @@
       </c>
       <c r="I133" s="32"/>
       <c r="J133" s="33" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="26" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B134" s="37" t="s">
         <v>75</v>
@@ -7991,13 +8310,13 @@
         <v>89</v>
       </c>
       <c r="D134" s="29" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E134" s="28" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="F134" s="28" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="G134" s="30" t="s">
         <v>93</v>
@@ -8007,27 +8326,27 @@
       </c>
       <c r="I134" s="32"/>
       <c r="J134" s="33" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="26" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B135" s="37" t="s">
         <v>75</v>
       </c>
       <c r="C135" s="28" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D135" s="29" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="E135" s="28" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="F135" s="28" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="G135" s="30" t="s">
         <v>93</v>
@@ -8037,12 +8356,12 @@
       </c>
       <c r="I135" s="32"/>
       <c r="J135" s="33" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="26" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B136" s="37" t="s">
         <v>75</v>
@@ -8051,13 +8370,13 @@
         <v>89</v>
       </c>
       <c r="D136" s="29" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="E136" s="28" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="F136" s="28" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="G136" s="30" t="s">
         <v>93</v>
@@ -8067,27 +8386,27 @@
       </c>
       <c r="I136" s="32"/>
       <c r="J136" s="33" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="26" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B137" s="37" t="s">
         <v>75</v>
       </c>
       <c r="C137" s="28" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D137" s="29" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="E137" s="28" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="F137" s="28" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="G137" s="30" t="s">
         <v>93</v>
@@ -8097,12 +8416,12 @@
       </c>
       <c r="I137" s="32"/>
       <c r="J137" s="33" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="26" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B138" s="37" t="s">
         <v>75</v>
@@ -8111,13 +8430,13 @@
         <v>89</v>
       </c>
       <c r="D138" s="29" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E138" s="28" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="F138" s="28" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="G138" s="30" t="s">
         <v>93</v>
@@ -8127,12 +8446,12 @@
       </c>
       <c r="I138" s="32"/>
       <c r="J138" s="33" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="26" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B139" s="37" t="s">
         <v>75</v>
@@ -8141,13 +8460,13 @@
         <v>89</v>
       </c>
       <c r="D139" s="29" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="E139" s="28" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F139" s="28" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="G139" s="30" t="s">
         <v>93</v>
@@ -8157,12 +8476,12 @@
       </c>
       <c r="I139" s="32"/>
       <c r="J139" s="33" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="26" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B140" s="37" t="s">
         <v>75</v>
@@ -8171,13 +8490,13 @@
         <v>141</v>
       </c>
       <c r="D140" s="29" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E140" s="28" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="F140" s="28" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G140" s="30" t="s">
         <v>93</v>
@@ -8187,27 +8506,27 @@
       </c>
       <c r="I140" s="32"/>
       <c r="J140" s="33" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="26" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B141" s="37" t="s">
         <v>75</v>
       </c>
       <c r="C141" s="28" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D141" s="29" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E141" s="28" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="G141" s="30" t="s">
         <v>93</v>
@@ -8217,12 +8536,12 @@
       </c>
       <c r="I141" s="32"/>
       <c r="J141" s="33" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="26" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="B142" s="37" t="s">
         <v>75</v>
@@ -8231,13 +8550,13 @@
         <v>89</v>
       </c>
       <c r="D142" s="29" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="E142" s="28" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="F142" s="28" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="G142" s="30" t="s">
         <v>134</v>
@@ -8247,12 +8566,12 @@
       </c>
       <c r="I142" s="32"/>
       <c r="J142" s="33" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="26" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B143" s="37" t="s">
         <v>75</v>
@@ -8261,13 +8580,13 @@
         <v>89</v>
       </c>
       <c r="D143" s="29" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="E143" s="28" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="F143" s="28" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="G143" s="30" t="s">
         <v>93</v>
@@ -8277,27 +8596,27 @@
       </c>
       <c r="I143" s="32"/>
       <c r="J143" s="33" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="26" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B144" s="37" t="s">
         <v>75</v>
       </c>
       <c r="C144" s="28" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D144" s="29" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="E144" s="28" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="F144" s="28" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="G144" s="30" t="s">
         <v>93</v>
@@ -8307,12 +8626,12 @@
       </c>
       <c r="I144" s="32"/>
       <c r="J144" s="33" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="26" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B145" s="37" t="s">
         <v>75</v>
@@ -8321,13 +8640,13 @@
         <v>141</v>
       </c>
       <c r="D145" s="29" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E145" s="28" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F145" s="28" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="G145" s="30" t="s">
         <v>93</v>
@@ -8337,12 +8656,12 @@
       </c>
       <c r="I145" s="32"/>
       <c r="J145" s="33" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="26" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B146" s="37" t="s">
         <v>75</v>
@@ -8351,13 +8670,13 @@
         <v>141</v>
       </c>
       <c r="D146" s="29" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="E146" s="28" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="F146" s="28" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="G146" s="30" t="s">
         <v>134</v>
@@ -8367,12 +8686,12 @@
       </c>
       <c r="I146" s="32"/>
       <c r="J146" s="33" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="26" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B147" s="37" t="s">
         <v>75</v>
@@ -8381,13 +8700,13 @@
         <v>89</v>
       </c>
       <c r="D147" s="29" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="E147" s="28" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="F147" s="28" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="G147" s="30" t="s">
         <v>134</v>
@@ -8397,95 +8716,14 @@
       </c>
       <c r="I147" s="32"/>
       <c r="J147" s="33" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="26" t="s">
-        <v>736</v>
-      </c>
-      <c r="B148" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C148" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="D148" s="29" t="s">
-        <v>757</v>
-      </c>
-      <c r="E148" s="28" t="s">
-        <v>758</v>
-      </c>
-      <c r="F148" s="28" t="s">
-        <v>759</v>
-      </c>
-      <c r="G148" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="H148" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I148" s="32"/>
-      <c r="J148" s="33"/>
-    </row>
-    <row r="149" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="26" t="s">
-        <v>742</v>
-      </c>
-      <c r="B149" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C149" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="D149" s="29" t="s">
         <v>760</v>
       </c>
-      <c r="E149" s="28" t="s">
-        <v>761</v>
-      </c>
-      <c r="F149" s="28" t="s">
-        <v>762</v>
-      </c>
-      <c r="G149" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="H149" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I149" s="32"/>
-      <c r="J149" s="33"/>
-    </row>
-    <row r="150" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="26" t="s">
-        <v>747</v>
-      </c>
-      <c r="B150" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C150" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="D150" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="E150" s="28" t="s">
-        <v>764</v>
-      </c>
-      <c r="F150" s="28" t="s">
-        <v>765</v>
-      </c>
-      <c r="G150" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="H150" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I150" s="32"/>
-      <c r="J150" s="33"/>
-    </row>
+    </row>
+    <row r="148" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="150" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:J150"/>
+  <autoFilter ref="A1:J147"/>
   <conditionalFormatting sqref="H2:H300">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"Đạt"</formula>

--- a/docs/rehearsal/checklist.xlsx
+++ b/docs/rehearsal/checklist.xlsx
@@ -26,12 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="763">
   <si>
     <t xml:space="preserve">StayGuard: checklist diễn tập (Gate 1)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cập nhật 03/10/2026 tối. Phạm vi: demo portfolio, không có khách thật; các dòng cần nhà nghỉ thật, tiền thật hoặc hạ tầng thật là Bỏ qua kèm lý do. Kết quả tự động (QA, make demo-check) ghi Đạt kèm ghi chú 'QA tự động &lt;ngày&gt;'; các dòng cần mắt người (GD-03 đến GD-07, TD-05, TD-08) chỉ nhận ghi chú và chờ bạn xem. TT-21, TT-22, TT-26 giữ Chờ thử lại vì test chưa phủ hết kỳ vọng. Đã gộp GL-13 đến GL-16 của phiên khác; các dòng trùng mã đã gỡ.</t>
+    <t xml:space="preserve">Cập nhật 03/10/2026 tối. Phạm vi: demo portfolio, không có khách thật; các dòng cần nhà nghỉ thật, tiền thật hoặc hạ tầng thật là Bỏ qua kèm lý do. Kết quả tự động (QA, make demo-check) ghi Đạt kèm ghi chú 'QA tự động &lt;ngày&gt;'; các dòng cần mắt người (GD-03 đến GD-07, TD-05, TD-08) chỉ nhận ghi chú và chờ bạn xem. TT-21, TT-22, TT-26 giữ Chờ thử lại vì test chưa phủ hết kỳ vọng. Đã gộp GL-13 đến GL-16 của phiên khác; các dòng trùng mã đã gỡ. Cập nhật 04/10/2026: make demo-check xanh 8/8 và CI GitHub xanh 9/9 (run #243).</t>
   </si>
   <si>
     <t xml:space="preserve">Cách dùng</t>
@@ -311,7 +311,8 @@
     <t xml:space="preserve">Cao</t>
   </si>
   <si>
-    <t xml:space="preserve">Số test đã tăng: make smoke hiện chạy 9 spec (WEB-1 báo 9 passed trên máy của lane, chưa phải bạn). Cập nhật kỳ vọng khi bạn thử.</t>
+    <t xml:space="preserve">Số test đã tăng: make smoke hiện chạy 9 spec (WEB-1 báo 9 passed trên máy của lane, chưa phải bạn). Cập nhật kỳ vọng khi bạn thử.
+make smoke xanh trong make demo-check (04/10/2026, QA tự động); nay chạy 10 spec.</t>
   </si>
   <si>
     <t xml:space="preserve">CB-02</t>
@@ -710,7 +711,8 @@
     <t xml:space="preserve">Màn tự hiện QR hết hạn, có nút tạo QR mới. Tiền chuyển vào mã cũ vẫn được ghi nhận khi SePay báo.</t>
   </si>
   <si>
-    <t xml:space="preserve">QA tự động 03/10/2026. QR không bao giờ chuyển EXPIRED theo thời gian: ExpirePending chỉ chạy khi tạo thanh toán mới, qrExpiryMinutes chỉ được lưu. Đề xuất: suy ra EXPIRED lúc đọc, giữ bản ghi PENDING để tiền về mã cũ vẫn khớp. Giao API-2.</t>
+    <t xml:space="preserve">QA tự động 03/10/2026. QR không bao giờ chuyển EXPIRED theo thời gian: ExpirePending chỉ chạy khi tạo thanh toán mới, qrExpiryMinutes chỉ được lưu. Đề xuất: suy ra EXPIRED lúc đọc, giữ bản ghi PENDING để tiền về mã cũ vẫn khớp. Giao API-2.
+QA tự động 04/10/2026: QR quá hạn trả EXPIRED (e640f86, suy ra lúc đọc), tiền về mã cũ vẫn khớp; e2e smoke.then-expiry của WEB-1 đạt, demo-check xanh.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-16</t>
@@ -807,7 +809,8 @@
   <si>
     <t xml:space="preserve">03/10 08:48: A102 bị kẹt, ô phòng mất loại thuê và giờ ở, không bấm vào được.
 Đã sửa một phần (WEB-1 f6add89): ô Chờ hoàn ₫X và nút Hoàn lại khách khi mở lại. Mới có unit test, chưa chạy với hoàn cọc thật. Thử lại sau rebuild.
-QA tự động đạt. Giữ Chờ thử lại vì kỳ vọng có 'dữ liệu cũ cũng xử lý được', test dùng nhà nghỉ mới.</t>
+QA tự động đạt. Giữ Chờ thử lại vì kỳ vọng có 'dữ liệu cũ cũng xử lý được', test dùng nhà nghỉ mới.
+demo-check 04/10 xanh. Vẫn chờ bạn thử với dữ liệu cũ.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-22</t>
@@ -824,7 +827,8 @@
   <si>
     <t xml:space="preserve">API-2 phải trả lời: giờ ra chốt lúc mở màn hay lúc xác nhận thanh toán.
 WEB-1 báo API chốt giờ ra lúc xác nhận thanh toán (rời màn mà chưa xác nhận thì lượt vẫn đang ở). Cần xác nhận lại với API-2 rồi thử tay.
-QA tự động đạt. Giữ Chờ thử lại cho tới khi API-2 xác nhận quy tắc giờ ra (WEB-1 báo: chốt lúc xác nhận thanh toán).</t>
+QA tự động đạt. Giữ Chờ thử lại cho tới khi API-2 xác nhận quy tắc giờ ra (WEB-1 báo: chốt lúc xác nhận thanh toán).
+demo-check 04/10 xanh. Vẫn chờ API-2 xác nhận quy tắc giờ ra.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-23</t>
@@ -889,7 +893,8 @@
   </si>
   <si>
     <t xml:space="preserve">03/10 08:42: A101 ghi cọc 0đ, phải thu 80.000đ. API-2 đối chiếu cọc lúc đọc và sửa dữ liệu cũ; WEB-1 đọc đúng trường. Gốc rễ chưa tái hiện được.
-QA tự động đạt trên nhà nghỉ mới. Gốc rễ ban đầu chưa tái hiện được nên giữ Chờ thử lại cho tới khi bạn mở lại màn trả phòng trên dữ liệu của bạn.</t>
+QA tự động đạt trên nhà nghỉ mới. Gốc rễ ban đầu chưa tái hiện được nên giữ Chờ thử lại cho tới khi bạn mở lại màn trả phòng trên dữ liệu của bạn.
+demo-check 04/10 xanh sau khi sửa test (đọc đúng dòng cọc; ảnh chụp thấy cọc ₫250,000). Vẫn chờ bạn mở lại màn trả phòng trên dữ liệu của bạn.</t>
   </si>
   <si>
     <t xml:space="preserve">TT-27</t>
@@ -1054,7 +1059,8 @@
     <t xml:space="preserve">Thấy số đếm, khoản chi, lý do, người bàn giao.</t>
   </si>
   <si>
-    <t xml:space="preserve">QA tự động 03/10/2026. Màn đối soát ca không nêu người bàn giao. Đề xuất: người đóng ca (tên, vai trò) và quỹ để lại; hệ thống không có người nhận ca. Giao API-2 và WEB-2.</t>
+    <t xml:space="preserve">QA tự động 03/10/2026. Màn đối soát ca không nêu người bàn giao. Đề xuất: người đóng ca (tên, vai trò) và quỹ để lại; hệ thống không có người nhận ca. Giao API-2 và WEB-2.
+04/10/2026: API trả closedByName, closedByRole, floatLeft (318d2a0, 3214b9d); màn Đối soát ca có Người bàn giao và Để lại két (WEB-2). QA tự động đạt. Chưa xem màn trên API thật: bạn mở Đối soát ca một lần rồi chuyển Đạt.</t>
   </si>
   <si>
     <t xml:space="preserve">CA-09</t>
@@ -1975,6 +1981,9 @@
     <t xml:space="preserve">Xanh. Gồm chữ ký, thời gian, chống trùng, giao dịch tiền ra.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bộ test webhook tự động là make test-api-int: xanh trong demo-check và trên CI #243 (04/10/2026).</t>
+  </si>
+  <si>
     <t xml:space="preserve">VH-01</t>
   </si>
   <si>
@@ -2169,6 +2178,9 @@
   </si>
   <si>
     <t xml:space="preserve">Cả 8 kiểm tra xanh: checks, lint, contracts, licenses, secrets, test-api, test-api-int, test-web.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI xanh 9/9 job (run #243, commit 92472f7, 04/10/2026): lint, checks, test-api, test-api-int, test-web, contracts, image, secrets, licenses. Repo public.</t>
   </si>
   <si>
     <t xml:space="preserve">GL-02</t>
@@ -2784,7 +2796,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="24">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2934,14 +2946,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE0DED8"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF5C2BD"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3564,7 +3568,7 @@
       </c>
       <c r="C5" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A5,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A5,Checklist!$H$2:$H$300,"Lỗi")</f>
@@ -3580,11 +3584,11 @@
       </c>
       <c r="G5" s="9" t="n">
         <f aca="false">B5-C5-D5-E5-F5</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="10" t="n">
         <f aca="false">IFERROR(C5/(B5-F5),0)</f>
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3597,11 +3601,11 @@
       </c>
       <c r="C6" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A6,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A6,Checklist!$H$2:$H$300,"Lỗi")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A6,Checklist!$H$2:$H$300,"Chờ thử lại")</f>
@@ -3617,7 +3621,7 @@
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">IFERROR(C6/(B6-F6),0)</f>
-        <v>0.851851851851852</v>
+        <v>0.888888888888889</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3634,11 +3638,11 @@
       </c>
       <c r="D7" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A7,Checklist!$H$2:$H$300,"Lỗi")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A7,Checklist!$H$2:$H$300,"Chờ thử lại")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A7,Checklist!$H$2:$H$300,"Bỏ qua")</f>
@@ -3861,7 +3865,7 @@
       </c>
       <c r="C14" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A14,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A14,Checklist!$H$2:$H$300,"Lỗi")</f>
@@ -3877,11 +3881,11 @@
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">B14-C14-D14-E14-F14</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="10" t="n">
         <f aca="false">IFERROR(C14/(B14-F14),0)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3960,7 +3964,7 @@
       </c>
       <c r="C17" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A17,Checklist!$H$2:$H$300,"Đạt")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
         <f aca="false">COUNTIFS(Checklist!$B$2:$B$300,$A17,Checklist!$H$2:$H$300,"Lỗi")</f>
@@ -3976,11 +3980,11 @@
       </c>
       <c r="G17" s="9" t="n">
         <f aca="false">B17-C17-D17-E17-F17</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H17" s="10" t="n">
         <f aca="false">IFERROR(C17/(B17-F17),0)</f>
-        <v>0</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3993,15 +3997,15 @@
       </c>
       <c r="C18" s="18" t="n">
         <f aca="false">SUM(C5:C17)</f>
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D18" s="18" t="n">
         <f aca="false">SUM(D5:D17)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
         <f aca="false">SUM(E5:E17)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">SUM(F5:F17)</f>
@@ -4009,11 +4013,11 @@
       </c>
       <c r="G18" s="18" t="n">
         <f aca="false">SUM(G5:G17)</f>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">IFERROR(C18/(B18-F18),0)</f>
-        <v>0.795275590551181</v>
+        <v>0.826771653543307</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4027,7 +4031,7 @@
       </c>
       <c r="B21" s="21" t="n">
         <f aca="false">COUNTIFS(Checklist!$G$2:$G$300,"Cao")-COUNTIFS(Checklist!$G$2:$G$300,"Cao",Checklist!$H$2:$H$300,"Đạt")-COUNTIFS(Checklist!$G$2:$G$300,"Cao",Checklist!$H$2:$H$300,"Bỏ qua")</f>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4036,7 +4040,7 @@
       </c>
       <c r="B22" s="21" t="n">
         <f aca="false">D18</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4168,9 +4172,11 @@
         <v>93</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="I2" s="32" t="n">
+        <v>46299</v>
+      </c>
       <c r="J2" s="33" t="s">
         <v>94</v>
       </c>
@@ -4952,10 +4958,10 @@
         <v>134</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="I27" s="32" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="J27" s="33" t="s">
         <v>219</v>
@@ -5646,11 +5652,9 @@
         <v>134</v>
       </c>
       <c r="H49" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="I49" s="32" t="n">
-        <v>46298</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="I49" s="32"/>
       <c r="J49" s="33" t="s">
         <v>325</v>
       </c>
@@ -7812,14 +7816,18 @@
         <v>93</v>
       </c>
       <c r="H117" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I117" s="32"/>
-      <c r="J117" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I117" s="32" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J117" s="33" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="26" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B118" s="27" t="s">
         <v>73</v>
@@ -7828,13 +7836,13 @@
         <v>89</v>
       </c>
       <c r="D118" s="29" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E118" s="28" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F118" s="28" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G118" s="30" t="s">
         <v>93</v>
@@ -7844,12 +7852,12 @@
       </c>
       <c r="I118" s="32"/>
       <c r="J118" s="33" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="26" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B119" s="27" t="s">
         <v>73</v>
@@ -7858,13 +7866,13 @@
         <v>89</v>
       </c>
       <c r="D119" s="29" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E119" s="28" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F119" s="28" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G119" s="30" t="s">
         <v>134</v>
@@ -7881,7 +7889,7 @@
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="26" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B120" s="27" t="s">
         <v>73</v>
@@ -7890,13 +7898,13 @@
         <v>89</v>
       </c>
       <c r="D120" s="29" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E120" s="28" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F120" s="28" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G120" s="30" t="s">
         <v>93</v>
@@ -7908,12 +7916,12 @@
         <v>46298</v>
       </c>
       <c r="J120" s="33" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="26" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B121" s="27" t="s">
         <v>73</v>
@@ -7922,13 +7930,13 @@
         <v>89</v>
       </c>
       <c r="D121" s="29" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E121" s="28" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F121" s="28" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G121" s="30" t="s">
         <v>93</v>
@@ -7938,12 +7946,12 @@
       </c>
       <c r="I121" s="32"/>
       <c r="J121" s="33" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="26" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B122" s="27" t="s">
         <v>73</v>
@@ -7952,13 +7960,13 @@
         <v>89</v>
       </c>
       <c r="D122" s="29" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E122" s="28" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F122" s="28" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G122" s="30" t="s">
         <v>93</v>
@@ -7975,7 +7983,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="26" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B123" s="27" t="s">
         <v>73</v>
@@ -7984,13 +7992,13 @@
         <v>89</v>
       </c>
       <c r="D123" s="29" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E123" s="28" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F123" s="28" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G123" s="30" t="s">
         <v>134</v>
@@ -8007,7 +8015,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="26" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B124" s="27" t="s">
         <v>73</v>
@@ -8016,13 +8024,13 @@
         <v>89</v>
       </c>
       <c r="D124" s="29" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E124" s="28" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F124" s="28" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G124" s="30" t="s">
         <v>145</v>
@@ -8032,12 +8040,12 @@
       </c>
       <c r="I124" s="32"/>
       <c r="J124" s="33" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="26" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B125" s="35" t="s">
         <v>74</v>
@@ -8046,13 +8054,13 @@
         <v>169</v>
       </c>
       <c r="D125" s="29" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E125" s="28" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F125" s="28" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G125" s="30" t="s">
         <v>93</v>
@@ -8065,7 +8073,7 @@
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="26" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B126" s="35" t="s">
         <v>74</v>
@@ -8074,13 +8082,13 @@
         <v>141</v>
       </c>
       <c r="D126" s="29" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E126" s="28" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F126" s="28" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G126" s="30" t="s">
         <v>134</v>
@@ -8093,7 +8101,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="26" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B127" s="35" t="s">
         <v>74</v>
@@ -8102,13 +8110,13 @@
         <v>141</v>
       </c>
       <c r="D127" s="29" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E127" s="28" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F127" s="28" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G127" s="30" t="s">
         <v>134</v>
@@ -8123,7 +8131,7 @@
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="26" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B128" s="35" t="s">
         <v>74</v>
@@ -8132,13 +8140,13 @@
         <v>141</v>
       </c>
       <c r="D128" s="29" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E128" s="28" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F128" s="28" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G128" s="30" t="s">
         <v>134</v>
@@ -8153,7 +8161,7 @@
     </row>
     <row r="129" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="26" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B129" s="35" t="s">
         <v>74</v>
@@ -8162,13 +8170,13 @@
         <v>169</v>
       </c>
       <c r="D129" s="29" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E129" s="28" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F129" s="28" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G129" s="30" t="s">
         <v>134</v>
@@ -8183,7 +8191,7 @@
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="26" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B130" s="35" t="s">
         <v>74</v>
@@ -8192,13 +8200,13 @@
         <v>130</v>
       </c>
       <c r="D130" s="29" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E130" s="28" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F130" s="28" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G130" s="30" t="s">
         <v>134</v>
@@ -8213,7 +8221,7 @@
     </row>
     <row r="131" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="26" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B131" s="35" t="s">
         <v>74</v>
@@ -8222,13 +8230,13 @@
         <v>169</v>
       </c>
       <c r="D131" s="29" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E131" s="28" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F131" s="28" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G131" s="30" t="s">
         <v>145</v>
@@ -8243,7 +8251,7 @@
     </row>
     <row r="132" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="26" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B132" s="37" t="s">
         <v>75</v>
@@ -8252,26 +8260,30 @@
         <v>89</v>
       </c>
       <c r="D132" s="29" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E132" s="28" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F132" s="28" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="G132" s="30" t="s">
         <v>93</v>
       </c>
       <c r="H132" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="I132" s="32"/>
-      <c r="J132" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I132" s="32" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J132" s="33" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="26" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B133" s="37" t="s">
         <v>75</v>
@@ -8280,13 +8292,13 @@
         <v>89</v>
       </c>
       <c r="D133" s="29" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E133" s="28" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="F133" s="28" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G133" s="30" t="s">
         <v>93</v>
@@ -8296,12 +8308,12 @@
       </c>
       <c r="I133" s="32"/>
       <c r="J133" s="33" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="26" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B134" s="37" t="s">
         <v>75</v>
@@ -8310,13 +8322,13 @@
         <v>89</v>
       </c>
       <c r="D134" s="29" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E134" s="28" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F134" s="28" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="G134" s="30" t="s">
         <v>93</v>
@@ -8326,12 +8338,12 @@
       </c>
       <c r="I134" s="32"/>
       <c r="J134" s="33" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="26" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B135" s="37" t="s">
         <v>75</v>
@@ -8340,13 +8352,13 @@
         <v>280</v>
       </c>
       <c r="D135" s="29" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E135" s="28" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="F135" s="28" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="G135" s="30" t="s">
         <v>93</v>
@@ -8356,12 +8368,12 @@
       </c>
       <c r="I135" s="32"/>
       <c r="J135" s="33" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="26" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B136" s="37" t="s">
         <v>75</v>
@@ -8370,13 +8382,13 @@
         <v>89</v>
       </c>
       <c r="D136" s="29" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E136" s="28" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="F136" s="28" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="G136" s="30" t="s">
         <v>93</v>
@@ -8386,12 +8398,12 @@
       </c>
       <c r="I136" s="32"/>
       <c r="J136" s="33" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="26" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B137" s="37" t="s">
         <v>75</v>
@@ -8400,13 +8412,13 @@
         <v>280</v>
       </c>
       <c r="D137" s="29" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E137" s="28" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="F137" s="28" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G137" s="30" t="s">
         <v>93</v>
@@ -8416,12 +8428,12 @@
       </c>
       <c r="I137" s="32"/>
       <c r="J137" s="33" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="26" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B138" s="37" t="s">
         <v>75</v>
@@ -8430,13 +8442,13 @@
         <v>89</v>
       </c>
       <c r="D138" s="29" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E138" s="28" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F138" s="28" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G138" s="30" t="s">
         <v>93</v>
@@ -8446,12 +8458,12 @@
       </c>
       <c r="I138" s="32"/>
       <c r="J138" s="33" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="26" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B139" s="37" t="s">
         <v>75</v>
@@ -8460,13 +8472,13 @@
         <v>89</v>
       </c>
       <c r="D139" s="29" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E139" s="28" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="F139" s="28" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="G139" s="30" t="s">
         <v>93</v>
@@ -8476,12 +8488,12 @@
       </c>
       <c r="I139" s="32"/>
       <c r="J139" s="33" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="26" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B140" s="37" t="s">
         <v>75</v>
@@ -8490,13 +8502,13 @@
         <v>141</v>
       </c>
       <c r="D140" s="29" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E140" s="28" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F140" s="28" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G140" s="30" t="s">
         <v>93</v>
@@ -8506,27 +8518,27 @@
       </c>
       <c r="I140" s="32"/>
       <c r="J140" s="33" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="26" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B141" s="37" t="s">
         <v>75</v>
       </c>
       <c r="C141" s="28" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D141" s="29" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E141" s="28" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="G141" s="30" t="s">
         <v>93</v>
@@ -8536,12 +8548,12 @@
       </c>
       <c r="I141" s="32"/>
       <c r="J141" s="33" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="26" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B142" s="37" t="s">
         <v>75</v>
@@ -8550,13 +8562,13 @@
         <v>89</v>
       </c>
       <c r="D142" s="29" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E142" s="28" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="F142" s="28" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G142" s="30" t="s">
         <v>134</v>
@@ -8566,12 +8578,12 @@
       </c>
       <c r="I142" s="32"/>
       <c r="J142" s="33" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="26" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B143" s="37" t="s">
         <v>75</v>
@@ -8580,13 +8592,13 @@
         <v>89</v>
       </c>
       <c r="D143" s="29" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E143" s="28" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="F143" s="28" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="G143" s="30" t="s">
         <v>93</v>
@@ -8596,27 +8608,27 @@
       </c>
       <c r="I143" s="32"/>
       <c r="J143" s="33" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="26" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B144" s="37" t="s">
         <v>75</v>
       </c>
       <c r="C144" s="28" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D144" s="29" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E144" s="28" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F144" s="28" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="G144" s="30" t="s">
         <v>93</v>
@@ -8626,12 +8638,12 @@
       </c>
       <c r="I144" s="32"/>
       <c r="J144" s="33" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="26" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B145" s="37" t="s">
         <v>75</v>
@@ -8640,13 +8652,13 @@
         <v>141</v>
       </c>
       <c r="D145" s="29" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E145" s="28" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F145" s="28" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G145" s="30" t="s">
         <v>93</v>
@@ -8656,12 +8668,12 @@
       </c>
       <c r="I145" s="32"/>
       <c r="J145" s="33" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="26" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B146" s="37" t="s">
         <v>75</v>
@@ -8670,13 +8682,13 @@
         <v>141</v>
       </c>
       <c r="D146" s="29" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E146" s="28" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="F146" s="28" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="G146" s="30" t="s">
         <v>134</v>
@@ -8686,12 +8698,12 @@
       </c>
       <c r="I146" s="32"/>
       <c r="J146" s="33" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="26" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B147" s="37" t="s">
         <v>75</v>
@@ -8700,13 +8712,13 @@
         <v>89</v>
       </c>
       <c r="D147" s="29" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E147" s="28" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="F147" s="28" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G147" s="30" t="s">
         <v>134</v>
@@ -8716,7 +8728,7 @@
       </c>
       <c r="I147" s="32"/>
       <c r="J147" s="33" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -8734,12 +8746,12 @@
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"Chờ thử lại"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>"Bỏ qua"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G300">
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>"Cao"</formula>
     </cfRule>
   </conditionalFormatting>
